--- a/ies-procesos/Informes-Gerencia-IES-2026.xlsx
+++ b/ies-procesos/Informes-Gerencia-IES-2026.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1 Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2 Ocupacion" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 Calendario" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4 Gestion mensual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="0 Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1 Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2 Ocupacion" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3 Calendario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4 Gestion mensual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5 Consolidado" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,6 +128,23 @@
       <b val="1"/>
       <color rgb="00DC2626"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B3A6B"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0064748B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001A2540"/>
+      <sz val="17"/>
     </font>
   </fonts>
   <fills count="15">
@@ -271,7 +290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -396,6 +415,44 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,6 +817,272 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="49" t="inlineStr">
+        <is>
+          <t>IES</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="50" t="inlineStr">
+        <is>
+          <t>Intelligent Electronic Solutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>INFORME DE GESTIÓN DE PROCESOS CONTABLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>Carga planificada, ocupación por posición y seguimiento mensual · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>CONTROL DEL DOCUMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>IES-CT-INF-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="53" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>Fecha de emisión</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
+        <is>
+          <t>10 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>Elaborado por</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>Cristian Bernal — Contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>Dirigido a</t>
+        </is>
+      </c>
+      <c r="C14" s="54" t="inlineStr">
+        <is>
+          <t>Gerencia · Supervisión · Recursos Humanos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>Periodicidad</t>
+        </is>
+      </c>
+      <c r="C15" s="54" t="inlineStr">
+        <is>
+          <t>Mensual, con corte al cierre de cada mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>Fuente de datos</t>
+        </is>
+      </c>
+      <c r="C16" s="54" t="inlineStr">
+        <is>
+          <t>Aplicación IES de seguimiento de procesos contables</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>Alcance</t>
+        </is>
+      </c>
+      <c r="C17" s="54" t="inlineStr">
+        <is>
+          <t>Ciclo contable mensual — cinco posiciones del proceso</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>CONTENIDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>1 Resumen</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="inlineStr">
+        <is>
+          <t>Carga anual por persona y concentración de la carga dentro del mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>2 Ocupacion</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>Días-tarea de cada posición en los doce meses del año</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>3 Calendario</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="inlineStr">
+        <is>
+          <t>Hitos del ciclo con fecha límite y nivel de criticidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>4 Gestion mensual</t>
+        </is>
+      </c>
+      <c r="C24" s="54" t="inlineStr">
+        <is>
+          <t>Formato de seguimiento del cumplimiento real, mes a mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>5 Consolidado</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>Resumen anual del cumplimiento, se alimenta de la hoja 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>NOTA METODOLÓGICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="56" t="inlineStr">
+        <is>
+          <t>·  Días-tarea: suma de los días que cada tarea permanece abierta en el mes. Mide exposición y simultaneidad, no horas trabajadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="56" t="inlineStr">
+        <is>
+          <t>·  Ocupación: porcentaje de días del período con al menos una tarea abierta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="56" t="inlineStr">
+        <is>
+          <t>·  Pico: máximo de tareas de una misma persona abiertas en un mismo día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="56" t="inlineStr">
+        <is>
+          <t>·  Las hojas 1, 2 y 3 reflejan la carga PLANIFICADA según el catálogo de procesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>·  La hoja 4 registra la EJECUCIÓN real y se diligencia al cierre de cada mes.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B33:G33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
@@ -1132,8 +1455,8 @@
           <t>El 30% de la carga del mes cae entre los días 8 y 14. Coincide con el cierre contable y con los cinco insumos del informe.</t>
         </is>
       </c>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
+      <c r="D24" s="57" t="n"/>
+      <c r="E24" s="58" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="24" t="inlineStr">
@@ -1146,8 +1469,8 @@
           <t>15 tareas simultáneas del equipo el día 10, 12, 13. Es el punto más tenso del ciclo.</t>
         </is>
       </c>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="58" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="24" t="inlineStr">
@@ -1160,8 +1483,8 @@
           <t>Pico de 7 tareas propias en un mismo día. Es la posición con la ventana más apretada del mes.</t>
         </is>
       </c>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="58" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="24" t="inlineStr">
@@ -1174,8 +1497,8 @@
           <t>Ocupación del 100%: tiene tareas abiertas todos los días del año por el registro diario de RC y RP.</t>
         </is>
       </c>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
+      <c r="D27" s="57" t="n"/>
+      <c r="E27" s="58" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="24" t="inlineStr">
@@ -1188,8 +1511,8 @@
           <t>Dos compromisos con fecha: definir viáticos de tarjeta (días 6 a 10) y dar feedback al informe (días 13 a 14).</t>
         </is>
       </c>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
+      <c r="D28" s="57" t="n"/>
+      <c r="E28" s="58" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1204,7 +1527,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1818,7 +2141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2394,7 +2717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2431,6 +2754,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
         <is>
@@ -2459,6 +2783,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="35" t="inlineStr">
         <is>
@@ -2612,6 +2937,7 @@
       </c>
       <c r="G16" s="23" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="35" t="inlineStr">
         <is>
@@ -2765,6 +3091,7 @@
       </c>
       <c r="G25" s="23" t="inlineStr"/>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" s="35" t="inlineStr">
         <is>
@@ -2918,6 +3245,7 @@
       </c>
       <c r="G34" s="23" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="B36" s="35" t="inlineStr">
         <is>
@@ -3071,6 +3399,7 @@
       </c>
       <c r="G43" s="23" t="inlineStr"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="B45" s="35" t="inlineStr">
         <is>
@@ -3224,6 +3553,7 @@
       </c>
       <c r="G52" s="23" t="inlineStr"/>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="B54" s="35" t="inlineStr">
         <is>
@@ -3377,6 +3707,7 @@
       </c>
       <c r="G61" s="23" t="inlineStr"/>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="B63" s="35" t="inlineStr">
         <is>
@@ -3530,6 +3861,7 @@
       </c>
       <c r="G70" s="23" t="inlineStr"/>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="B72" s="35" t="inlineStr">
         <is>
@@ -3683,6 +4015,7 @@
       </c>
       <c r="G79" s="23" t="inlineStr"/>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="B81" s="35" t="inlineStr">
         <is>
@@ -3836,6 +4169,7 @@
       </c>
       <c r="G88" s="23" t="inlineStr"/>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="B90" s="35" t="inlineStr">
         <is>
@@ -3989,6 +4323,7 @@
       </c>
       <c r="G97" s="23" t="inlineStr"/>
     </row>
+    <row r="98"/>
     <row r="99">
       <c r="B99" s="35" t="inlineStr">
         <is>
@@ -4142,6 +4477,7 @@
       </c>
       <c r="G106" s="23" t="inlineStr"/>
     </row>
+    <row r="107"/>
     <row r="108">
       <c r="B108" s="35" t="inlineStr">
         <is>
@@ -4299,4 +4635,379 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Consolidado anual de cumplimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Se alimenta automáticamente de la hoja 4 · no requiere diligenciamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="59" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="C4" s="59" t="inlineStr">
+        <is>
+          <t>Programadas</t>
+        </is>
+      </c>
+      <c r="D4" s="59" t="inlineStr">
+        <is>
+          <t>Completadas</t>
+        </is>
+      </c>
+      <c r="E4" s="59" t="inlineStr">
+        <is>
+          <t>Cumplimiento</t>
+        </is>
+      </c>
+      <c r="F4" s="59" t="inlineStr">
+        <is>
+          <t>Vencidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="C5" s="60">
+        <f>'4 Gestion mensual'!C16</f>
+        <v/>
+      </c>
+      <c r="D5" s="60">
+        <f>'4 Gestion mensual'!D16</f>
+        <v/>
+      </c>
+      <c r="E5" s="61">
+        <f>IFERROR(D5/C5,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="60">
+        <f>'4 Gestion mensual'!F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="C6" s="60">
+        <f>'4 Gestion mensual'!C25</f>
+        <v/>
+      </c>
+      <c r="D6" s="60">
+        <f>'4 Gestion mensual'!D25</f>
+        <v/>
+      </c>
+      <c r="E6" s="61">
+        <f>IFERROR(D6/C6,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="60">
+        <f>'4 Gestion mensual'!F25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="C7" s="60">
+        <f>'4 Gestion mensual'!C34</f>
+        <v/>
+      </c>
+      <c r="D7" s="60">
+        <f>'4 Gestion mensual'!D34</f>
+        <v/>
+      </c>
+      <c r="E7" s="61">
+        <f>IFERROR(D7/C7,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="60">
+        <f>'4 Gestion mensual'!F34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="C8" s="60">
+        <f>'4 Gestion mensual'!C43</f>
+        <v/>
+      </c>
+      <c r="D8" s="60">
+        <f>'4 Gestion mensual'!D43</f>
+        <v/>
+      </c>
+      <c r="E8" s="61">
+        <f>IFERROR(D8/C8,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="60">
+        <f>'4 Gestion mensual'!F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C9" s="60">
+        <f>'4 Gestion mensual'!C52</f>
+        <v/>
+      </c>
+      <c r="D9" s="60">
+        <f>'4 Gestion mensual'!D52</f>
+        <v/>
+      </c>
+      <c r="E9" s="61">
+        <f>IFERROR(D9/C9,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="60">
+        <f>'4 Gestion mensual'!F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="C10" s="60">
+        <f>'4 Gestion mensual'!C61</f>
+        <v/>
+      </c>
+      <c r="D10" s="60">
+        <f>'4 Gestion mensual'!D61</f>
+        <v/>
+      </c>
+      <c r="E10" s="61">
+        <f>IFERROR(D10/C10,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="60">
+        <f>'4 Gestion mensual'!F61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="C11" s="60">
+        <f>'4 Gestion mensual'!C70</f>
+        <v/>
+      </c>
+      <c r="D11" s="60">
+        <f>'4 Gestion mensual'!D70</f>
+        <v/>
+      </c>
+      <c r="E11" s="61">
+        <f>IFERROR(D11/C11,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="60">
+        <f>'4 Gestion mensual'!F70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="C12" s="60">
+        <f>'4 Gestion mensual'!C79</f>
+        <v/>
+      </c>
+      <c r="D12" s="60">
+        <f>'4 Gestion mensual'!D79</f>
+        <v/>
+      </c>
+      <c r="E12" s="61">
+        <f>IFERROR(D12/C12,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="60">
+        <f>'4 Gestion mensual'!F79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="C13" s="60">
+        <f>'4 Gestion mensual'!C88</f>
+        <v/>
+      </c>
+      <c r="D13" s="60">
+        <f>'4 Gestion mensual'!D88</f>
+        <v/>
+      </c>
+      <c r="E13" s="61">
+        <f>IFERROR(D13/C13,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="60">
+        <f>'4 Gestion mensual'!F88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="C14" s="60">
+        <f>'4 Gestion mensual'!C97</f>
+        <v/>
+      </c>
+      <c r="D14" s="60">
+        <f>'4 Gestion mensual'!D97</f>
+        <v/>
+      </c>
+      <c r="E14" s="61">
+        <f>IFERROR(D14/C14,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="60">
+        <f>'4 Gestion mensual'!F97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="C15" s="60">
+        <f>'4 Gestion mensual'!C106</f>
+        <v/>
+      </c>
+      <c r="D15" s="60">
+        <f>'4 Gestion mensual'!D106</f>
+        <v/>
+      </c>
+      <c r="E15" s="61">
+        <f>IFERROR(D15/C15,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="60">
+        <f>'4 Gestion mensual'!F106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="C16" s="60">
+        <f>'4 Gestion mensual'!C115</f>
+        <v/>
+      </c>
+      <c r="D16" s="60">
+        <f>'4 Gestion mensual'!D115</f>
+        <v/>
+      </c>
+      <c r="E16" s="61">
+        <f>IFERROR(D16/C16,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="60">
+        <f>'4 Gestion mensual'!F115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>TOTAL AÑO</t>
+        </is>
+      </c>
+      <c r="C17" s="62">
+        <f>SUM(C5:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="62">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="63">
+        <f>IFERROR(D17/C17,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="62">
+        <f>SUM(F5:F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="64" t="inlineStr">
+        <is>
+          <t>Las celdas de esta hoja se calculan solas. Para que muestren datos, diligencie primero la hoja 4.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait"/>
+</worksheet>
 </file>
--- a/ies-procesos/Informes-Gerencia-IES-2026.xlsx
+++ b/ies-procesos/Informes-Gerencia-IES-2026.xlsx
@@ -10,9 +10,10 @@
     <sheet name="0 Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1 Resumen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2 Ocupacion" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3 Calendario" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4 Gestion mensual" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="5 Consolidado" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2b Saturacion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3 Calendario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="4 Gestion mensual" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5 Consolidado" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -145,6 +148,18 @@
       <b val="1"/>
       <color rgb="001A2540"/>
       <sz val="17"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="15">
@@ -290,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,6 +465,74 @@
     </xf>
     <xf numFmtId="9" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -819,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -827,6 +910,7 @@
     <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="49" t="inlineStr">
         <is>
@@ -841,6 +925,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="51" t="inlineStr">
         <is>
@@ -855,6 +940,8 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="52" t="inlineStr">
         <is>
@@ -958,6 +1045,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="52" t="inlineStr">
         <is>
@@ -990,78 +1079,92 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="55" t="inlineStr">
-        <is>
-          <t>3 Calendario</t>
-        </is>
-      </c>
-      <c r="C23" s="54" t="inlineStr">
-        <is>
-          <t>Hitos del ciclo con fecha límite y nivel de criticidad</t>
+      <c r="B23" s="65" t="inlineStr">
+        <is>
+          <t>2b Saturacion</t>
+        </is>
+      </c>
+      <c r="C23" s="66" t="inlineStr">
+        <is>
+          <t>Frentes de trabajo simultáneos por día hábil — evidencia del nivel de saturación</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="55" t="inlineStr">
         <is>
-          <t>4 Gestion mensual</t>
+          <t>3 Calendario</t>
         </is>
       </c>
       <c r="C24" s="54" t="inlineStr">
         <is>
-          <t>Formato de seguimiento del cumplimiento real, mes a mes</t>
+          <t>Hitos del ciclo con fecha límite y nivel de criticidad</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="55" t="inlineStr">
         <is>
+          <t>4 Gestion mensual</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>Formato de seguimiento del cumplimiento real, mes a mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="55" t="inlineStr">
+        <is>
           <t>5 Consolidado</t>
         </is>
       </c>
-      <c r="C25" s="54" t="inlineStr">
+      <c r="C26" s="54" t="inlineStr">
         <is>
           <t>Resumen anual del cumplimiento, se alimenta de la hoja 4</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="52" t="inlineStr">
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" s="52" t="inlineStr">
         <is>
           <t>NOTA METODOLÓGICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="56" t="inlineStr">
-        <is>
-          <t>·  Días-tarea: suma de los días que cada tarea permanece abierta en el mes. Mide exposición y simultaneidad, no horas trabajadas.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="56" t="inlineStr">
         <is>
-          <t>·  Ocupación: porcentaje de días del período con al menos una tarea abierta.</t>
+          <t>·  Días-tarea: suma de los días que cada tarea permanece abierta en el mes. Mide exposición y simultaneidad, no horas trabajadas.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="56" t="inlineStr">
         <is>
-          <t>·  Pico: máximo de tareas de una misma persona abiertas en un mismo día.</t>
+          <t>·  Ocupación: porcentaje de días del período con al menos una tarea abierta.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="56" t="inlineStr">
         <is>
-          <t>·  Las hojas 1, 2 y 3 reflejan la carga PLANIFICADA según el catálogo de procesos.</t>
+          <t>·  Pico: máximo de tareas de una misma persona abiertas en un mismo día.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="56" t="inlineStr">
+        <is>
+          <t>·  Las hojas 1, 2 y 3 reflejan la carga PLANIFICADA según el catálogo de procesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="56" t="inlineStr">
         <is>
           <t>·  La hoja 4 registra la EJECUCIÓN real y se diligencia al cierre de cada mes.</t>
         </is>
@@ -1118,7 +1221,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>CARGA PLANIFICADA DEL AÑO</t>
         </is>
@@ -1166,23 +1269,23 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>Tesorera</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="60" t="n">
         <v>72</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="60" t="n">
         <v>1196</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="61" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
@@ -1194,23 +1297,23 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="54" t="inlineStr">
         <is>
           <t>Aux. Contable</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="60" t="n">
         <v>120</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="60" t="n">
         <v>1003</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="61" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="n">
@@ -1222,23 +1325,23 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>Contador</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="60" t="n">
         <v>174</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="60" t="n">
         <v>719</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="61" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="11" t="n">
@@ -1250,23 +1353,23 @@
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="54" t="inlineStr">
         <is>
           <t>Insumos Facturación</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="60" t="n">
         <v>24</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="60" t="n">
         <v>401</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="61" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="11" t="n">
@@ -1278,23 +1381,23 @@
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>Automatización / Siigo</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="60" t="n">
         <v>60</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="60" t="n">
         <v>269</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="61" t="n">
         <v>0.5726027397260274</v>
       </c>
       <c r="G10" s="11" t="n">
@@ -1305,7 +1408,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>CONCENTRACIÓN DE LA CARGA EN EL MES</t>
         </is>
@@ -1334,111 +1437,111 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>Días 1 a 7</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="60" t="n">
         <v>63</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="61" t="n">
         <v>0.2093023255813954</v>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="54" t="inlineStr">
         <is>
           <t>Apertura del mes y facturación</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>Días 8 a 14</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="60" t="n">
         <v>90</v>
       </c>
       <c r="D16" s="19" t="n">
         <v>0.2990033222591362</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="54" t="inlineStr">
         <is>
           <t>Cierre contable e insumos del informe</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t>Días 15 a 21</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="60" t="n">
         <v>54</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="61" t="n">
         <v>0.1794019933554817</v>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
         <is>
           <t>Entrega a Gerencia, socios y RADIAN</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>Días 22 a 28</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="60" t="n">
         <v>64</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="61" t="n">
         <v>0.212624584717608</v>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>Causaciones y nómina de segunda quincena</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
         <is>
           <t>Días 29 al cierre</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="60" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="61" t="n">
         <v>0.09966777408637874</v>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="54" t="inlineStr">
         <is>
           <t>Desembolsos y archivo plano</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="53" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="62" t="n">
         <v>301</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="63" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="23" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="52" t="inlineStr">
         <is>
           <t>HALLAZGOS</t>
         </is>
@@ -1573,7 +1676,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>DÍAS-TAREA POR MES</t>
         </is>
@@ -1693,7 +1796,7 @@
       <c r="N6" s="28" t="n">
         <v>102</v>
       </c>
-      <c r="O6" s="21" t="n">
+      <c r="O6" s="62" t="n">
         <v>1196</v>
       </c>
     </row>
@@ -1739,7 +1842,7 @@
       <c r="N7" s="28" t="n">
         <v>85</v>
       </c>
-      <c r="O7" s="21" t="n">
+      <c r="O7" s="62" t="n">
         <v>1003</v>
       </c>
     </row>
@@ -1785,7 +1888,7 @@
       <c r="N8" s="30" t="n">
         <v>57</v>
       </c>
-      <c r="O8" s="21" t="n">
+      <c r="O8" s="62" t="n">
         <v>719</v>
       </c>
     </row>
@@ -1831,7 +1934,7 @@
       <c r="N9" s="33" t="n">
         <v>34</v>
       </c>
-      <c r="O9" s="21" t="n">
+      <c r="O9" s="62" t="n">
         <v>401</v>
       </c>
     </row>
@@ -1841,43 +1944,43 @@
           <t>Edgar</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="60" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="60" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="60" t="n">
         <v>22</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="K10" s="9" t="n">
+      <c r="K10" s="60" t="n">
         <v>22</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="60" t="n">
         <v>22</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="60" t="n">
         <v>23</v>
       </c>
-      <c r="O10" s="21" t="n">
+      <c r="O10" s="62" t="n">
         <v>269</v>
       </c>
     </row>
@@ -1887,48 +1990,48 @@
           <t>EQUIPO</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="62" t="n">
         <v>308</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="62" t="n">
         <v>271</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="62" t="n">
         <v>308</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="62" t="n">
         <v>292</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="62" t="n">
         <v>308</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="62" t="n">
         <v>292</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="62" t="n">
         <v>308</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="62" t="n">
         <v>301</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="62" t="n">
         <v>299</v>
       </c>
-      <c r="L11" s="21" t="n">
+      <c r="L11" s="62" t="n">
         <v>301</v>
       </c>
-      <c r="M11" s="21" t="n">
+      <c r="M11" s="62" t="n">
         <v>299</v>
       </c>
-      <c r="N11" s="21" t="n">
+      <c r="N11" s="62" t="n">
         <v>301</v>
       </c>
-      <c r="O11" s="21" t="n">
+      <c r="O11" s="62" t="n">
         <v>3588</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>OCUPACIÓN Y PICO POR PERSONA</t>
         </is>
@@ -1977,20 +2080,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="60" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="60" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="11" t="n">
@@ -2006,20 +2109,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="60" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
@@ -2035,20 +2138,20 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="60" t="n">
         <v>14</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="60" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="11" t="n">
@@ -2064,20 +2167,20 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="60" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="61" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="11" t="n">
@@ -2093,20 +2196,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="60" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="60" t="inlineStr">
         <is>
           <t>18 de 31</t>
         </is>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="61" t="n">
         <v>0.5806451612903226</v>
       </c>
       <c r="F20" s="11" t="n">
@@ -2122,14 +2225,14 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="40" t="inlineStr">
+      <c r="B23" s="64" t="inlineStr">
         <is>
           <t>Días-tarea: suma de los días que cada tarea permanece abierta. Mide exposición, no horas trabajadas.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="40" t="inlineStr">
+      <c r="B24" s="64" t="inlineStr">
         <is>
           <t>Pico: máximo de tareas de esa persona abiertas en un mismo día. Verde hasta 3, ámbar 4 y 5, rojo desde 6.</t>
         </is>
@@ -2142,6 +2245,918 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="6.5" customWidth="1" min="3" max="3"/>
+    <col width="6.5" customWidth="1" min="4" max="4"/>
+    <col width="6.5" customWidth="1" min="5" max="5"/>
+    <col width="6.5" customWidth="1" min="6" max="6"/>
+    <col width="6.5" customWidth="1" min="7" max="7"/>
+    <col width="6.5" customWidth="1" min="8" max="8"/>
+    <col width="6.5" customWidth="1" min="9" max="9"/>
+    <col width="6.5" customWidth="1" min="10" max="10"/>
+    <col width="6.5" customWidth="1" min="11" max="11"/>
+    <col width="6.5" customWidth="1" min="12" max="12"/>
+    <col width="6.5" customWidth="1" min="13" max="13"/>
+    <col width="6.5" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Nivel de saturación del equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Frentes de trabajo abiertos simultáneamente, medidos contra días hábiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="67" t="inlineStr">
+        <is>
+          <t>RESUMEN ANUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Frentes por
+día hábil</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Días del año con
+3 o más frentes</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Días del año con
+4 o más frentes</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Fines de semana
+con tarea abierta</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Lectura</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="68" t="inlineStr">
+        <is>
+          <t>Isnardi Sanches</t>
+        </is>
+      </c>
+      <c r="C6" s="69" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="D6" s="70" t="n">
+        <v>365</v>
+      </c>
+      <c r="E6" s="71" t="n">
+        <v>77</v>
+      </c>
+      <c r="F6" s="71" t="n">
+        <v>104</v>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Sin un solo día de holgura en todo el año</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="68" t="inlineStr">
+        <is>
+          <t>Luis Amador</t>
+        </is>
+      </c>
+      <c r="C7" s="69" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="D7" s="72" t="n">
+        <v>202</v>
+      </c>
+      <c r="E7" s="71" t="n">
+        <v>71</v>
+      </c>
+      <c r="F7" s="71" t="n">
+        <v>104</v>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>Más de la mitad del mes en simultaneidad alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="68" t="inlineStr">
+        <is>
+          <t>Cristian Bernal</t>
+        </is>
+      </c>
+      <c r="C8" s="73" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D8" s="72" t="n">
+        <v>72</v>
+      </c>
+      <c r="E8" s="71" t="n">
+        <v>48</v>
+      </c>
+      <c r="F8" s="71" t="n">
+        <v>104</v>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>Menos días, pero con la mayor densidad por día</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>Beatriz</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D9" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="71" t="n">
+        <v>104</v>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>Carga continua de baja simultaneidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="68" t="inlineStr">
+        <is>
+          <t>Edgar Metaute</t>
+        </is>
+      </c>
+      <c r="C10" s="74" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="D10" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="71" t="n">
+        <v>59</v>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>Intervenciones puntuales, no continuas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>FRENTES ABIERTOS POR DÍA HÁBIL, MES A MES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Ago</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="68" t="inlineStr">
+        <is>
+          <t>Isnardi</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="D15" s="75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E15" s="75" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="F15" s="75" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G15" s="75" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="H15" s="75" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="I15" s="75" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="J15" s="75" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="K15" s="75" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L15" s="75" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M15" s="75" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="N15" s="75" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="O15" s="76" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="D16" s="75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E16" s="75" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="F16" s="75" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G16" s="75" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H16" s="75" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I16" s="75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J16" s="75" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K16" s="75" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="L16" s="75" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M16" s="75" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N16" s="75" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O16" s="76" t="n">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="68" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="C17" s="77" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D17" s="77" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E17" s="77" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="F17" s="77" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G17" s="77" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H17" s="77" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I17" s="77" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="J17" s="77" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="K17" s="77" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L17" s="77" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M17" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="78" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O17" s="76" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="68" t="inlineStr">
+        <is>
+          <t>Beatriz</t>
+        </is>
+      </c>
+      <c r="C18" s="78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D18" s="78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E18" s="78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F18" s="78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G18" s="78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H18" s="78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" s="78" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J18" s="78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K18" s="78" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L18" s="78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M18" s="78" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N18" s="78" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O18" s="76" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="68" t="inlineStr">
+        <is>
+          <t>Edgar</t>
+        </is>
+      </c>
+      <c r="C19" s="78" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D19" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="78" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F19" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="78" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H19" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="78" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K19" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="78" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M19" s="78" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="76" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="79" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="80" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="E20" s="80" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="80" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="G20" s="80" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="H20" s="80" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="I20" s="80" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="J20" s="80" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="K20" s="80" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="L20" s="80" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="M20" s="80" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="N20" s="80" t="n">
+        <v>13.09</v>
+      </c>
+      <c r="O20" s="76" t="n">
+        <v>13.76</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="81" t="inlineStr">
+        <is>
+          <t>Días hábiles</t>
+        </is>
+      </c>
+      <c r="C21" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" s="82" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="F21" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="G21" s="82" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="I21" s="82" t="n">
+        <v>23</v>
+      </c>
+      <c r="J21" s="82" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="L21" s="82" t="n">
+        <v>22</v>
+      </c>
+      <c r="M21" s="82" t="n">
+        <v>21</v>
+      </c>
+      <c r="N21" s="82" t="n">
+        <v>23</v>
+      </c>
+      <c r="O21" s="83" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>DÍAS DEL MES CON 3 O MÁS FRENTES ABIERTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Posición</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Ene</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Abr</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Ago</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>Dic</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="68" t="inlineStr">
+        <is>
+          <t>Isnardi</t>
+        </is>
+      </c>
+      <c r="C25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="D25" s="70" t="n">
+        <v>28</v>
+      </c>
+      <c r="E25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="F25" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="H25" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="J25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="K25" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="L25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="M25" s="70" t="n">
+        <v>30</v>
+      </c>
+      <c r="N25" s="70" t="n">
+        <v>31</v>
+      </c>
+      <c r="O25" s="84" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="C26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" s="85" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="H26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="I26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="J26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="K26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="L26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="M26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="N26" s="85" t="n">
+        <v>17</v>
+      </c>
+      <c r="O26" s="84" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="68" t="inlineStr">
+        <is>
+          <t>Cristian</t>
+        </is>
+      </c>
+      <c r="C27" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="L27" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="M27" s="71" t="n">
+        <v>7</v>
+      </c>
+      <c r="N27" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="84" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="86" t="inlineStr">
+        <is>
+          <t>HALLAZGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="87" t="inlineStr">
+        <is>
+          <t>·  Tesorería registra 3 o más frentes abiertos los 365 días del año, incluidos los 104 días de fin de semana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="87" t="inlineStr">
+        <is>
+          <t>·  No existe un solo día del calendario en que Tesorería opere con menos de tres asuntos simultáneos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="87" t="inlineStr">
+        <is>
+          <t>·  El Auxiliar Contable está en esa condición 202 días al año; Contaduría 72 días, de ellos 48 con cuatro o más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="87" t="inlineStr">
+        <is>
+          <t>·  El equipo sostiene entre 13 y 15 frentes por día hábil todos los meses: la diferencia entre el mes más y menos cargado no llega al 12%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>QUÉ MIDE Y QUÉ NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="88" t="inlineStr">
+        <is>
+          <t>·  Mide simultaneidad: cuántos asuntos distintos permanecen abiertos a la vez, con su costo de atención y cambio de contexto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="88" t="inlineStr">
+        <is>
+          <t>·  NO mide horas trabajadas. Para cuantificar horas se requiere registro de tiempos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="88" t="inlineStr">
+        <is>
+          <t>·  Días hábiles contados de lunes a viernes, sin descontar festivos. El cálculo es conservador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="88" t="inlineStr">
+        <is>
+          <t>·  Semáforo: verde por debajo de 2,5 frentes · ámbar entre 2,5 y 3,5 · rojo desde 3,5.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B40:O40"/>
+    <mergeCell ref="B39:O39"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="B33:O33"/>
+    <mergeCell ref="B34:O34"/>
+    <mergeCell ref="B37:O37"/>
+    <mergeCell ref="B31:O31"/>
+    <mergeCell ref="B32:O32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2210,7 +3225,7 @@
           <t>1 al 5</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="54" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
@@ -2220,7 +3235,7 @@
           <t>Emisión de facturas electrónicas</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="60" t="inlineStr">
         <is>
           <t>Día 5</t>
         </is>
@@ -2237,7 +3252,7 @@
           <t>3 al 9</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -2247,7 +3262,7 @@
           <t>Conciliación bancaria</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="60" t="inlineStr">
         <is>
           <t>Día 9</t>
         </is>
@@ -2264,7 +3279,7 @@
           <t>6 al 10</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="54" t="inlineStr">
         <is>
           <t>Luis + Edgar</t>
         </is>
@@ -2274,7 +3289,7 @@
           <t>Conciliación de tarjeta y definición de viáticos</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>Día 10</t>
         </is>
@@ -2291,7 +3306,7 @@
           <t>10 al 13</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -2301,7 +3316,7 @@
           <t>Causación de seguridad social</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="60" t="inlineStr">
         <is>
           <t>Día 13</t>
         </is>
@@ -2318,7 +3333,7 @@
           <t>10 al 14</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="54" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -2328,7 +3343,7 @@
           <t>Causación de nómina primera quincena</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>Día 14</t>
         </is>
@@ -2345,7 +3360,7 @@
           <t>10 al 14</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="54" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -2355,7 +3370,7 @@
           <t>Cierre contable y retención en la fuente</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="60" t="inlineStr">
         <is>
           <t>Día 14</t>
         </is>
@@ -2372,7 +3387,7 @@
           <t>9 al 13</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="54" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -2382,7 +3397,7 @@
           <t>Insumos del informe: flujo, cartera, recaudo, EESF, ER</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>Día 13</t>
         </is>
@@ -2399,7 +3414,7 @@
           <t>10 al 12</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="54" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
@@ -2409,7 +3424,7 @@
           <t>Comentarios comerciales al informe</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="60" t="inlineStr">
         <is>
           <t>Día 12</t>
         </is>
@@ -2426,7 +3441,7 @@
           <t>13 al 15</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="54" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
@@ -2436,7 +3451,7 @@
           <t>Pago de seguridad social</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>Día 15</t>
         </is>
@@ -2453,7 +3468,7 @@
           <t>13 al 14</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
@@ -2463,7 +3478,7 @@
           <t>Feedback del informe antes de socios</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="60" t="inlineStr">
         <is>
           <t>Día 14</t>
         </is>
@@ -2480,7 +3495,7 @@
           <t>14 al 16</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="54" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
@@ -2490,7 +3505,7 @@
           <t>Desembolso de nómina primera quincena</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>Día 16</t>
         </is>
@@ -2507,7 +3522,7 @@
           <t>13 al 15</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="54" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -2517,7 +3532,7 @@
           <t>Entrega del dashboard a Gerencia</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="60" t="inlineStr">
         <is>
           <t>Día 15</t>
         </is>
@@ -2534,7 +3549,7 @@
           <t>15 al 20</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="54" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -2544,7 +3559,7 @@
           <t>Proceso con socios</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>Día 20</t>
         </is>
@@ -2561,7 +3576,7 @@
           <t>15 al 21</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="54" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -2571,7 +3586,7 @@
           <t>Declaración de IVA (meses del bimestre)</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="60" t="inlineStr">
         <is>
           <t>Día 21</t>
         </is>
@@ -2588,7 +3603,7 @@
           <t>15 al 25</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="54" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -2598,7 +3613,7 @@
           <t>Validación RADIAN</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>Día 25</t>
         </is>
@@ -2615,7 +3630,7 @@
           <t>25 al 29</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="54" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -2625,7 +3640,7 @@
           <t>Causación de nómina segunda quincena</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="60" t="inlineStr">
         <is>
           <t>Día 29</t>
         </is>
@@ -2642,7 +3657,7 @@
           <t>26 al cierre</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="54" t="inlineStr">
         <is>
           <t>Luis + Edgar</t>
         </is>
@@ -2652,7 +3667,7 @@
           <t>Archivo plano para facturar el día 1</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="60" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
@@ -2669,7 +3684,7 @@
           <t>29 al cierre</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="54" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
@@ -2679,7 +3694,7 @@
           <t>Desembolso de nómina segunda quincena</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="60" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
@@ -2691,21 +3706,21 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="64" t="inlineStr">
         <is>
           <t>Legal: tiene vencimiento de ley, no admite aplazamiento.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="40" t="inlineStr">
+      <c r="B26" s="64" t="inlineStr">
         <is>
           <t>Alta: si se retrasa, frena a otra persona del equipo.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="64" t="inlineStr">
         <is>
           <t>Media: afecta solo al proceso propio.</t>
         </is>
@@ -2717,7 +3732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2754,36 +3769,34 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="52" t="inlineStr">
         <is>
           <t>CÓMO SE DILIGENCIA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>·  Al cierre de cada mes, tomar de la aplicación el número de tareas completadas por persona.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="56" t="inlineStr">
         <is>
           <t>·  Escribir ese número en las celdas de fondo amarillo. Las demás columnas se calculan solas.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="56" t="inlineStr">
         <is>
           <t>·  La columna Programadas ya viene con el dato del mes correspondiente.</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="35" t="inlineStr">
         <is>
@@ -2829,16 +3842,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="48" t="n"/>
-      <c r="E11" s="10">
+      <c r="E11" s="61">
         <f>IFERROR(D11/C11,"")</f>
         <v/>
       </c>
@@ -2846,16 +3859,16 @@
       <c r="G11" s="25" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D12" s="48" t="n"/>
-      <c r="E12" s="10">
+      <c r="E12" s="61">
         <f>IFERROR(D12/C12,"")</f>
         <v/>
       </c>
@@ -2863,16 +3876,16 @@
       <c r="G12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="60" t="n">
         <v>15</v>
       </c>
       <c r="D13" s="48" t="n"/>
-      <c r="E13" s="10">
+      <c r="E13" s="61">
         <f>IFERROR(D13/C13,"")</f>
         <v/>
       </c>
@@ -2880,16 +3893,16 @@
       <c r="G13" s="25" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D14" s="48" t="n"/>
-      <c r="E14" s="10">
+      <c r="E14" s="61">
         <f>IFERROR(D14/C14,"")</f>
         <v/>
       </c>
@@ -2897,16 +3910,16 @@
       <c r="G14" s="25" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="48" t="n"/>
-      <c r="E15" s="10">
+      <c r="E15" s="61">
         <f>IFERROR(D15/C15,"")</f>
         <v/>
       </c>
@@ -2914,30 +3927,29 @@
       <c r="G15" s="25" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="62">
         <f>SUM(C11:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="62">
         <f>SUM(D11:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="63">
         <f>IFERROR(D16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="62">
         <f>SUM(F11:F15)</f>
         <v/>
       </c>
       <c r="G16" s="23" t="inlineStr"/>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="B18" s="35" t="inlineStr">
         <is>
@@ -2983,16 +3995,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D20" s="48" t="n"/>
-      <c r="E20" s="10">
+      <c r="E20" s="61">
         <f>IFERROR(D20/C20,"")</f>
         <v/>
       </c>
@@ -3000,16 +4012,16 @@
       <c r="G20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D21" s="48" t="n"/>
-      <c r="E21" s="10">
+      <c r="E21" s="61">
         <f>IFERROR(D21/C21,"")</f>
         <v/>
       </c>
@@ -3017,16 +4029,16 @@
       <c r="G21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="60" t="n">
         <v>14</v>
       </c>
       <c r="D22" s="48" t="n"/>
-      <c r="E22" s="10">
+      <c r="E22" s="61">
         <f>IFERROR(D22/C22,"")</f>
         <v/>
       </c>
@@ -3034,16 +4046,16 @@
       <c r="G22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="48" t="n"/>
-      <c r="E23" s="10">
+      <c r="E23" s="61">
         <f>IFERROR(D23/C23,"")</f>
         <v/>
       </c>
@@ -3051,16 +4063,16 @@
       <c r="G23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="48" t="n"/>
-      <c r="E24" s="10">
+      <c r="E24" s="61">
         <f>IFERROR(D24/C24,"")</f>
         <v/>
       </c>
@@ -3068,30 +4080,29 @@
       <c r="G24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="62">
         <f>SUM(C20:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="62">
         <f>SUM(D20:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="63">
         <f>IFERROR(D25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="62">
         <f>SUM(F20:F24)</f>
         <v/>
       </c>
       <c r="G25" s="23" t="inlineStr"/>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="B27" s="35" t="inlineStr">
         <is>
@@ -3137,16 +4148,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D29" s="48" t="n"/>
-      <c r="E29" s="10">
+      <c r="E29" s="61">
         <f>IFERROR(D29/C29,"")</f>
         <v/>
       </c>
@@ -3154,16 +4165,16 @@
       <c r="G29" s="25" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C30" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D30" s="48" t="n"/>
-      <c r="E30" s="10">
+      <c r="E30" s="61">
         <f>IFERROR(D30/C30,"")</f>
         <v/>
       </c>
@@ -3171,16 +4182,16 @@
       <c r="G30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C31" s="60" t="n">
         <v>15</v>
       </c>
       <c r="D31" s="48" t="n"/>
-      <c r="E31" s="10">
+      <c r="E31" s="61">
         <f>IFERROR(D31/C31,"")</f>
         <v/>
       </c>
@@ -3188,16 +4199,16 @@
       <c r="G31" s="25" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C32" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="48" t="n"/>
-      <c r="E32" s="10">
+      <c r="E32" s="61">
         <f>IFERROR(D32/C32,"")</f>
         <v/>
       </c>
@@ -3205,16 +4216,16 @@
       <c r="G32" s="25" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D33" s="48" t="n"/>
-      <c r="E33" s="10">
+      <c r="E33" s="61">
         <f>IFERROR(D33/C33,"")</f>
         <v/>
       </c>
@@ -3222,30 +4233,29 @@
       <c r="G33" s="25" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="62">
         <f>SUM(C29:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="21">
+      <c r="D34" s="62">
         <f>SUM(D29:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="63">
         <f>IFERROR(D34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="62">
         <f>SUM(F29:F33)</f>
         <v/>
       </c>
       <c r="G34" s="23" t="inlineStr"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="B36" s="35" t="inlineStr">
         <is>
@@ -3291,16 +4301,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D38" s="48" t="n"/>
-      <c r="E38" s="10">
+      <c r="E38" s="61">
         <f>IFERROR(D38/C38,"")</f>
         <v/>
       </c>
@@ -3308,16 +4318,16 @@
       <c r="G38" s="25" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n">
+      <c r="C39" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D39" s="48" t="n"/>
-      <c r="E39" s="10">
+      <c r="E39" s="61">
         <f>IFERROR(D39/C39,"")</f>
         <v/>
       </c>
@@ -3325,16 +4335,16 @@
       <c r="G39" s="25" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n">
+      <c r="C40" s="60" t="n">
         <v>14</v>
       </c>
       <c r="D40" s="48" t="n"/>
-      <c r="E40" s="10">
+      <c r="E40" s="61">
         <f>IFERROR(D40/C40,"")</f>
         <v/>
       </c>
@@ -3342,16 +4352,16 @@
       <c r="G40" s="25" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C41" s="9" t="n">
+      <c r="C41" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D41" s="48" t="n"/>
-      <c r="E41" s="10">
+      <c r="E41" s="61">
         <f>IFERROR(D41/C41,"")</f>
         <v/>
       </c>
@@ -3359,16 +4369,16 @@
       <c r="G41" s="25" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C42" s="9" t="n">
+      <c r="C42" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D42" s="48" t="n"/>
-      <c r="E42" s="10">
+      <c r="E42" s="61">
         <f>IFERROR(D42/C42,"")</f>
         <v/>
       </c>
@@ -3376,30 +4386,29 @@
       <c r="G42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C43" s="21">
+      <c r="C43" s="62">
         <f>SUM(C38:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="62">
         <f>SUM(D38:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="63">
         <f>IFERROR(D43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="21">
+      <c r="F43" s="62">
         <f>SUM(F38:F42)</f>
         <v/>
       </c>
       <c r="G43" s="23" t="inlineStr"/>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="B45" s="35" t="inlineStr">
         <is>
@@ -3445,16 +4454,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B47" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D47" s="48" t="n"/>
-      <c r="E47" s="10">
+      <c r="E47" s="61">
         <f>IFERROR(D47/C47,"")</f>
         <v/>
       </c>
@@ -3462,16 +4471,16 @@
       <c r="G47" s="25" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C48" s="9" t="n">
+      <c r="C48" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D48" s="48" t="n"/>
-      <c r="E48" s="10">
+      <c r="E48" s="61">
         <f>IFERROR(D48/C48,"")</f>
         <v/>
       </c>
@@ -3479,16 +4488,16 @@
       <c r="G48" s="25" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n">
+      <c r="C49" s="60" t="n">
         <v>15</v>
       </c>
       <c r="D49" s="48" t="n"/>
-      <c r="E49" s="10">
+      <c r="E49" s="61">
         <f>IFERROR(D49/C49,"")</f>
         <v/>
       </c>
@@ -3496,16 +4505,16 @@
       <c r="G49" s="25" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n">
+      <c r="C50" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D50" s="48" t="n"/>
-      <c r="E50" s="10">
+      <c r="E50" s="61">
         <f>IFERROR(D50/C50,"")</f>
         <v/>
       </c>
@@ -3513,16 +4522,16 @@
       <c r="G50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C51" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D51" s="48" t="n"/>
-      <c r="E51" s="10">
+      <c r="E51" s="61">
         <f>IFERROR(D51/C51,"")</f>
         <v/>
       </c>
@@ -3530,30 +4539,29 @@
       <c r="G51" s="25" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B52" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="62">
         <f>SUM(C47:C51)</f>
         <v/>
       </c>
-      <c r="D52" s="21">
+      <c r="D52" s="62">
         <f>SUM(D47:D51)</f>
         <v/>
       </c>
-      <c r="E52" s="22">
+      <c r="E52" s="63">
         <f>IFERROR(D52/C52,"")</f>
         <v/>
       </c>
-      <c r="F52" s="21">
+      <c r="F52" s="62">
         <f>SUM(F47:F51)</f>
         <v/>
       </c>
       <c r="G52" s="23" t="inlineStr"/>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="B54" s="35" t="inlineStr">
         <is>
@@ -3599,16 +4607,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C56" s="9" t="n">
+      <c r="C56" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D56" s="48" t="n"/>
-      <c r="E56" s="10">
+      <c r="E56" s="61">
         <f>IFERROR(D56/C56,"")</f>
         <v/>
       </c>
@@ -3616,16 +4624,16 @@
       <c r="G56" s="25" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B57" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C57" s="9" t="n">
+      <c r="C57" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D57" s="48" t="n"/>
-      <c r="E57" s="10">
+      <c r="E57" s="61">
         <f>IFERROR(D57/C57,"")</f>
         <v/>
       </c>
@@ -3633,16 +4641,16 @@
       <c r="G57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C58" s="9" t="n">
+      <c r="C58" s="60" t="n">
         <v>14</v>
       </c>
       <c r="D58" s="48" t="n"/>
-      <c r="E58" s="10">
+      <c r="E58" s="61">
         <f>IFERROR(D58/C58,"")</f>
         <v/>
       </c>
@@ -3650,16 +4658,16 @@
       <c r="G58" s="25" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C59" s="9" t="n">
+      <c r="C59" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D59" s="48" t="n"/>
-      <c r="E59" s="10">
+      <c r="E59" s="61">
         <f>IFERROR(D59/C59,"")</f>
         <v/>
       </c>
@@ -3667,16 +4675,16 @@
       <c r="G59" s="25" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B60" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C60" s="9" t="n">
+      <c r="C60" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D60" s="48" t="n"/>
-      <c r="E60" s="10">
+      <c r="E60" s="61">
         <f>IFERROR(D60/C60,"")</f>
         <v/>
       </c>
@@ -3684,30 +4692,29 @@
       <c r="G60" s="25" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="20" t="inlineStr">
+      <c r="B61" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C61" s="21">
+      <c r="C61" s="62">
         <f>SUM(C56:C60)</f>
         <v/>
       </c>
-      <c r="D61" s="21">
+      <c r="D61" s="62">
         <f>SUM(D56:D60)</f>
         <v/>
       </c>
-      <c r="E61" s="22">
+      <c r="E61" s="63">
         <f>IFERROR(D61/C61,"")</f>
         <v/>
       </c>
-      <c r="F61" s="21">
+      <c r="F61" s="62">
         <f>SUM(F56:F60)</f>
         <v/>
       </c>
       <c r="G61" s="23" t="inlineStr"/>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="B63" s="35" t="inlineStr">
         <is>
@@ -3753,16 +4760,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C65" s="9" t="n">
+      <c r="C65" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D65" s="48" t="n"/>
-      <c r="E65" s="10">
+      <c r="E65" s="61">
         <f>IFERROR(D65/C65,"")</f>
         <v/>
       </c>
@@ -3770,16 +4777,16 @@
       <c r="G65" s="25" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C66" s="9" t="n">
+      <c r="C66" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D66" s="48" t="n"/>
-      <c r="E66" s="10">
+      <c r="E66" s="61">
         <f>IFERROR(D66/C66,"")</f>
         <v/>
       </c>
@@ -3787,16 +4794,16 @@
       <c r="G66" s="25" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B67" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C67" s="9" t="n">
+      <c r="C67" s="60" t="n">
         <v>15</v>
       </c>
       <c r="D67" s="48" t="n"/>
-      <c r="E67" s="10">
+      <c r="E67" s="61">
         <f>IFERROR(D67/C67,"")</f>
         <v/>
       </c>
@@ -3804,16 +4811,16 @@
       <c r="G67" s="25" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C68" s="9" t="n">
+      <c r="C68" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D68" s="48" t="n"/>
-      <c r="E68" s="10">
+      <c r="E68" s="61">
         <f>IFERROR(D68/C68,"")</f>
         <v/>
       </c>
@@ -3821,16 +4828,16 @@
       <c r="G68" s="25" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C69" s="9" t="n">
+      <c r="C69" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D69" s="48" t="n"/>
-      <c r="E69" s="10">
+      <c r="E69" s="61">
         <f>IFERROR(D69/C69,"")</f>
         <v/>
       </c>
@@ -3838,30 +4845,29 @@
       <c r="G69" s="25" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C70" s="21">
+      <c r="C70" s="62">
         <f>SUM(C65:C69)</f>
         <v/>
       </c>
-      <c r="D70" s="21">
+      <c r="D70" s="62">
         <f>SUM(D65:D69)</f>
         <v/>
       </c>
-      <c r="E70" s="22">
+      <c r="E70" s="63">
         <f>IFERROR(D70/C70,"")</f>
         <v/>
       </c>
-      <c r="F70" s="21">
+      <c r="F70" s="62">
         <f>SUM(F65:F69)</f>
         <v/>
       </c>
       <c r="G70" s="23" t="inlineStr"/>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="B72" s="35" t="inlineStr">
         <is>
@@ -3907,16 +4913,16 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C74" s="9" t="n">
+      <c r="C74" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D74" s="48" t="n"/>
-      <c r="E74" s="10">
+      <c r="E74" s="61">
         <f>IFERROR(D74/C74,"")</f>
         <v/>
       </c>
@@ -3924,16 +4930,16 @@
       <c r="G74" s="25" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C75" s="9" t="n">
+      <c r="C75" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D75" s="48" t="n"/>
-      <c r="E75" s="10">
+      <c r="E75" s="61">
         <f>IFERROR(D75/C75,"")</f>
         <v/>
       </c>
@@ -3941,16 +4947,16 @@
       <c r="G75" s="25" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C76" s="9" t="n">
+      <c r="C76" s="60" t="n">
         <v>14</v>
       </c>
       <c r="D76" s="48" t="n"/>
-      <c r="E76" s="10">
+      <c r="E76" s="61">
         <f>IFERROR(D76/C76,"")</f>
         <v/>
       </c>
@@ -3958,16 +4964,16 @@
       <c r="G76" s="25" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C77" s="9" t="n">
+      <c r="C77" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D77" s="48" t="n"/>
-      <c r="E77" s="10">
+      <c r="E77" s="61">
         <f>IFERROR(D77/C77,"")</f>
         <v/>
       </c>
@@ -3975,16 +4981,16 @@
       <c r="G77" s="25" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C78" s="9" t="n">
+      <c r="C78" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D78" s="48" t="n"/>
-      <c r="E78" s="10">
+      <c r="E78" s="61">
         <f>IFERROR(D78/C78,"")</f>
         <v/>
       </c>
@@ -3992,30 +4998,29 @@
       <c r="G78" s="25" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C79" s="21">
+      <c r="C79" s="62">
         <f>SUM(C74:C78)</f>
         <v/>
       </c>
-      <c r="D79" s="21">
+      <c r="D79" s="62">
         <f>SUM(D74:D78)</f>
         <v/>
       </c>
-      <c r="E79" s="22">
+      <c r="E79" s="63">
         <f>IFERROR(D79/C79,"")</f>
         <v/>
       </c>
-      <c r="F79" s="21">
+      <c r="F79" s="62">
         <f>SUM(F74:F78)</f>
         <v/>
       </c>
       <c r="G79" s="23" t="inlineStr"/>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="B81" s="35" t="inlineStr">
         <is>
@@ -4061,16 +5066,16 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C83" s="9" t="n">
+      <c r="C83" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D83" s="48" t="n"/>
-      <c r="E83" s="10">
+      <c r="E83" s="61">
         <f>IFERROR(D83/C83,"")</f>
         <v/>
       </c>
@@ -4078,16 +5083,16 @@
       <c r="G83" s="25" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C84" s="9" t="n">
+      <c r="C84" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D84" s="48" t="n"/>
-      <c r="E84" s="10">
+      <c r="E84" s="61">
         <f>IFERROR(D84/C84,"")</f>
         <v/>
       </c>
@@ -4095,16 +5100,16 @@
       <c r="G84" s="25" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="7" t="inlineStr">
+      <c r="B85" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C85" s="9" t="n">
+      <c r="C85" s="60" t="n">
         <v>15</v>
       </c>
       <c r="D85" s="48" t="n"/>
-      <c r="E85" s="10">
+      <c r="E85" s="61">
         <f>IFERROR(D85/C85,"")</f>
         <v/>
       </c>
@@ -4112,16 +5117,16 @@
       <c r="G85" s="25" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C86" s="9" t="n">
+      <c r="C86" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D86" s="48" t="n"/>
-      <c r="E86" s="10">
+      <c r="E86" s="61">
         <f>IFERROR(D86/C86,"")</f>
         <v/>
       </c>
@@ -4129,16 +5134,16 @@
       <c r="G86" s="25" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C87" s="9" t="n">
+      <c r="C87" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D87" s="48" t="n"/>
-      <c r="E87" s="10">
+      <c r="E87" s="61">
         <f>IFERROR(D87/C87,"")</f>
         <v/>
       </c>
@@ -4146,30 +5151,29 @@
       <c r="G87" s="25" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="20" t="inlineStr">
+      <c r="B88" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C88" s="21">
+      <c r="C88" s="62">
         <f>SUM(C83:C87)</f>
         <v/>
       </c>
-      <c r="D88" s="21">
+      <c r="D88" s="62">
         <f>SUM(D83:D87)</f>
         <v/>
       </c>
-      <c r="E88" s="22">
+      <c r="E88" s="63">
         <f>IFERROR(D88/C88,"")</f>
         <v/>
       </c>
-      <c r="F88" s="21">
+      <c r="F88" s="62">
         <f>SUM(F83:F87)</f>
         <v/>
       </c>
       <c r="G88" s="23" t="inlineStr"/>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="B90" s="35" t="inlineStr">
         <is>
@@ -4215,16 +5219,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C92" s="9" t="n">
+      <c r="C92" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D92" s="48" t="n"/>
-      <c r="E92" s="10">
+      <c r="E92" s="61">
         <f>IFERROR(D92/C92,"")</f>
         <v/>
       </c>
@@ -4232,16 +5236,16 @@
       <c r="G92" s="25" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C93" s="9" t="n">
+      <c r="C93" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D93" s="48" t="n"/>
-      <c r="E93" s="10">
+      <c r="E93" s="61">
         <f>IFERROR(D93/C93,"")</f>
         <v/>
       </c>
@@ -4249,16 +5253,16 @@
       <c r="G93" s="25" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C94" s="9" t="n">
+      <c r="C94" s="60" t="n">
         <v>14</v>
       </c>
       <c r="D94" s="48" t="n"/>
-      <c r="E94" s="10">
+      <c r="E94" s="61">
         <f>IFERROR(D94/C94,"")</f>
         <v/>
       </c>
@@ -4266,16 +5270,16 @@
       <c r="G94" s="25" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B95" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C95" s="9" t="n">
+      <c r="C95" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D95" s="48" t="n"/>
-      <c r="E95" s="10">
+      <c r="E95" s="61">
         <f>IFERROR(D95/C95,"")</f>
         <v/>
       </c>
@@ -4283,16 +5287,16 @@
       <c r="G95" s="25" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C96" s="9" t="n">
+      <c r="C96" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D96" s="48" t="n"/>
-      <c r="E96" s="10">
+      <c r="E96" s="61">
         <f>IFERROR(D96/C96,"")</f>
         <v/>
       </c>
@@ -4300,30 +5304,29 @@
       <c r="G96" s="25" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="20" t="inlineStr">
+      <c r="B97" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C97" s="21">
+      <c r="C97" s="62">
         <f>SUM(C92:C96)</f>
         <v/>
       </c>
-      <c r="D97" s="21">
+      <c r="D97" s="62">
         <f>SUM(D92:D96)</f>
         <v/>
       </c>
-      <c r="E97" s="22">
+      <c r="E97" s="63">
         <f>IFERROR(D97/C97,"")</f>
         <v/>
       </c>
-      <c r="F97" s="21">
+      <c r="F97" s="62">
         <f>SUM(F92:F96)</f>
         <v/>
       </c>
       <c r="G97" s="23" t="inlineStr"/>
     </row>
-    <row r="98"/>
     <row r="99">
       <c r="B99" s="35" t="inlineStr">
         <is>
@@ -4369,16 +5372,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C101" s="9" t="n">
+      <c r="C101" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D101" s="48" t="n"/>
-      <c r="E101" s="10">
+      <c r="E101" s="61">
         <f>IFERROR(D101/C101,"")</f>
         <v/>
       </c>
@@ -4386,16 +5389,16 @@
       <c r="G101" s="25" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C102" s="9" t="n">
+      <c r="C102" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D102" s="48" t="n"/>
-      <c r="E102" s="10">
+      <c r="E102" s="61">
         <f>IFERROR(D102/C102,"")</f>
         <v/>
       </c>
@@ -4403,16 +5406,16 @@
       <c r="G102" s="25" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B103" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C103" s="9" t="n">
+      <c r="C103" s="60" t="n">
         <v>15</v>
       </c>
       <c r="D103" s="48" t="n"/>
-      <c r="E103" s="10">
+      <c r="E103" s="61">
         <f>IFERROR(D103/C103,"")</f>
         <v/>
       </c>
@@ -4420,16 +5423,16 @@
       <c r="G103" s="25" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C104" s="9" t="n">
+      <c r="C104" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D104" s="48" t="n"/>
-      <c r="E104" s="10">
+      <c r="E104" s="61">
         <f>IFERROR(D104/C104,"")</f>
         <v/>
       </c>
@@ -4437,16 +5440,16 @@
       <c r="G104" s="25" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C105" s="9" t="n">
+      <c r="C105" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D105" s="48" t="n"/>
-      <c r="E105" s="10">
+      <c r="E105" s="61">
         <f>IFERROR(D105/C105,"")</f>
         <v/>
       </c>
@@ -4454,30 +5457,29 @@
       <c r="G105" s="25" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="20" t="inlineStr">
+      <c r="B106" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C106" s="21">
+      <c r="C106" s="62">
         <f>SUM(C101:C105)</f>
         <v/>
       </c>
-      <c r="D106" s="21">
+      <c r="D106" s="62">
         <f>SUM(D101:D105)</f>
         <v/>
       </c>
-      <c r="E106" s="22">
+      <c r="E106" s="63">
         <f>IFERROR(D106/C106,"")</f>
         <v/>
       </c>
-      <c r="F106" s="21">
+      <c r="F106" s="62">
         <f>SUM(F101:F105)</f>
         <v/>
       </c>
       <c r="G106" s="23" t="inlineStr"/>
     </row>
-    <row r="107"/>
     <row r="108">
       <c r="B108" s="35" t="inlineStr">
         <is>
@@ -4523,16 +5525,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="55" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C110" s="9" t="n">
+      <c r="C110" s="60" t="n">
         <v>6</v>
       </c>
       <c r="D110" s="48" t="n"/>
-      <c r="E110" s="10">
+      <c r="E110" s="61">
         <f>IFERROR(D110/C110,"")</f>
         <v/>
       </c>
@@ -4540,16 +5542,16 @@
       <c r="G110" s="25" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="55" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C111" s="9" t="n">
+      <c r="C111" s="60" t="n">
         <v>10</v>
       </c>
       <c r="D111" s="48" t="n"/>
-      <c r="E111" s="10">
+      <c r="E111" s="61">
         <f>IFERROR(D111/C111,"")</f>
         <v/>
       </c>
@@ -4557,16 +5559,16 @@
       <c r="G111" s="25" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="7" t="inlineStr">
+      <c r="B112" s="55" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C112" s="9" t="n">
+      <c r="C112" s="60" t="n">
         <v>14</v>
       </c>
       <c r="D112" s="48" t="n"/>
-      <c r="E112" s="10">
+      <c r="E112" s="61">
         <f>IFERROR(D112/C112,"")</f>
         <v/>
       </c>
@@ -4574,16 +5576,16 @@
       <c r="G112" s="25" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="55" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C113" s="9" t="n">
+      <c r="C113" s="60" t="n">
         <v>2</v>
       </c>
       <c r="D113" s="48" t="n"/>
-      <c r="E113" s="10">
+      <c r="E113" s="61">
         <f>IFERROR(D113/C113,"")</f>
         <v/>
       </c>
@@ -4591,16 +5593,16 @@
       <c r="G113" s="25" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="55" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C114" s="9" t="n">
+      <c r="C114" s="60" t="n">
         <v>5</v>
       </c>
       <c r="D114" s="48" t="n"/>
-      <c r="E114" s="10">
+      <c r="E114" s="61">
         <f>IFERROR(D114/C114,"")</f>
         <v/>
       </c>
@@ -4608,24 +5610,24 @@
       <c r="G114" s="25" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="20" t="inlineStr">
+      <c r="B115" s="53" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C115" s="21">
+      <c r="C115" s="62">
         <f>SUM(C110:C114)</f>
         <v/>
       </c>
-      <c r="D115" s="21">
+      <c r="D115" s="62">
         <f>SUM(D110:D114)</f>
         <v/>
       </c>
-      <c r="E115" s="22">
+      <c r="E115" s="63">
         <f>IFERROR(D115/C115,"")</f>
         <v/>
       </c>
-      <c r="F115" s="21">
+      <c r="F115" s="62">
         <f>SUM(F110:F114)</f>
         <v/>
       </c>
@@ -4637,7 +5639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/ies-procesos/Informes-Gerencia-IES-2026.xlsx
+++ b/ies-procesos/Informes-Gerencia-IES-2026.xlsx
@@ -305,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -385,9 +385,6 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -451,91 +448,68 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -900,285 +874,286 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="B2:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="48" t="inlineStr">
         <is>
           <t>IES</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t>Intelligent Electronic Solutions</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>INFORME DE GESTIÓN DE PROCESOS CONTABLES</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="50" t="inlineStr">
-        <is>
-          <t>Carga planificada, ocupación por posición y seguimiento mensual · 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8"/>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>Carga planificada, saturación por posición y seguimiento mensual · 2026</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>CONTROL DEL DOCUMENTO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="53" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="C10" s="54" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>IES-CT-INF-001</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="53" t="inlineStr">
+      <c r="B11" s="52" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="C11" s="54" t="inlineStr">
-        <is>
-          <t>1.0</t>
+      <c r="C11" s="53" t="inlineStr">
+        <is>
+          <t>1.1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="53" t="inlineStr">
+      <c r="B12" s="52" t="inlineStr">
         <is>
           <t>Fecha de emisión</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr">
+      <c r="C12" s="53" t="inlineStr">
         <is>
           <t>10 de agosto de 2026</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="53" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>Elaborado por</t>
         </is>
       </c>
-      <c r="C13" s="54" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>Cristian Bernal — Contador</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="53" t="inlineStr">
+      <c r="B14" s="52" t="inlineStr">
         <is>
           <t>Dirigido a</t>
         </is>
       </c>
-      <c r="C14" s="54" t="inlineStr">
+      <c r="C14" s="53" t="inlineStr">
         <is>
           <t>Gerencia · Supervisión · Recursos Humanos</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="53" t="inlineStr">
+      <c r="B15" s="52" t="inlineStr">
         <is>
           <t>Periodicidad</t>
         </is>
       </c>
-      <c r="C15" s="54" t="inlineStr">
+      <c r="C15" s="53" t="inlineStr">
         <is>
           <t>Mensual, con corte al cierre de cada mes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="53" t="inlineStr">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>Fuente de datos</t>
         </is>
       </c>
-      <c r="C16" s="54" t="inlineStr">
+      <c r="C16" s="53" t="inlineStr">
         <is>
           <t>Aplicación IES de seguimiento de procesos contables</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="53" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>Alcance</t>
         </is>
       </c>
-      <c r="C17" s="54" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t>Ciclo contable mensual — cinco posiciones del proceso</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>CONTENIDO</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="55" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>1 Resumen</t>
         </is>
       </c>
-      <c r="C21" s="54" t="inlineStr">
+      <c r="C21" s="53" t="inlineStr">
         <is>
           <t>Carga anual por persona y concentración de la carga dentro del mes</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>2 Ocupacion</t>
         </is>
       </c>
-      <c r="C22" s="54" t="inlineStr">
+      <c r="C22" s="53" t="inlineStr">
         <is>
           <t>Días-tarea de cada posición en los doce meses del año</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="65" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>2b Saturacion</t>
         </is>
       </c>
-      <c r="C23" s="66" t="inlineStr">
+      <c r="C23" s="53" t="inlineStr">
         <is>
           <t>Frentes de trabajo simultáneos por día hábil — evidencia del nivel de saturación</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="54" t="inlineStr">
         <is>
           <t>3 Calendario</t>
         </is>
       </c>
-      <c r="C24" s="54" t="inlineStr">
+      <c r="C24" s="53" t="inlineStr">
         <is>
           <t>Hitos del ciclo con fecha límite y nivel de criticidad</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="55" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
         <is>
           <t>4 Gestion mensual</t>
         </is>
       </c>
-      <c r="C25" s="54" t="inlineStr">
+      <c r="C25" s="53" t="inlineStr">
         <is>
           <t>Formato de seguimiento del cumplimiento real, mes a mes</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="55" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>5 Consolidado</t>
         </is>
       </c>
-      <c r="C26" s="54" t="inlineStr">
+      <c r="C26" s="53" t="inlineStr">
         <is>
           <t>Resumen anual del cumplimiento, se alimenta de la hoja 4</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
-      <c r="B29" s="52" t="inlineStr">
+      <c r="B29" s="51" t="inlineStr">
         <is>
           <t>NOTA METODOLÓGICA</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="56" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>·  Días-tarea: suma de los días que cada tarea permanece abierta en el mes. Mide exposición y simultaneidad, no horas trabajadas.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="56" t="inlineStr">
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>·  Frentes por día hábil: días-tarea divididos entre los días hábiles del período (lunes a viernes, sin descontar festivos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>·  Ocupación: porcentaje de días del período con al menos una tarea abierta.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="56" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="55" t="inlineStr">
         <is>
           <t>·  Pico: máximo de tareas de una misma persona abiertas en un mismo día.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="56" t="inlineStr">
-        <is>
-          <t>·  Las hojas 1, 2 y 3 reflejan la carga PLANIFICADA según el catálogo de procesos.</t>
-        </is>
-      </c>
-    </row>
     <row r="34">
-      <c r="B34" s="56" t="inlineStr">
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>·  Las hojas 1, 2, 2b y 3 reflejan la carga PLANIFICADA según el catálogo de procesos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>·  La hoja 4 registra la EJECUCIÓN real y se diligencia al cierre de cada mes.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="B34:G34"/>
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B35:G35"/>
     <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B29:G29"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1221,7 +1196,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>CARGA PLANIFICADA DEL AÑO</t>
         </is>
@@ -1269,23 +1244,23 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C6" s="54" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Tesorera</t>
         </is>
       </c>
-      <c r="D6" s="60" t="n">
+      <c r="D6" s="9" t="n">
         <v>72</v>
       </c>
-      <c r="E6" s="60" t="n">
+      <c r="E6" s="9" t="n">
         <v>1196</v>
       </c>
-      <c r="F6" s="61" t="n">
+      <c r="F6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
@@ -1297,23 +1272,23 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n"/>
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Aux. Contable</t>
         </is>
       </c>
-      <c r="D7" s="60" t="n">
+      <c r="D7" s="9" t="n">
         <v>120</v>
       </c>
-      <c r="E7" s="60" t="n">
+      <c r="E7" s="9" t="n">
         <v>1003</v>
       </c>
-      <c r="F7" s="61" t="n">
+      <c r="F7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="n">
@@ -1325,27 +1300,27 @@
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C8" s="54" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Contador</t>
         </is>
       </c>
-      <c r="D8" s="60" t="n">
+      <c r="D8" s="9" t="n">
         <v>174</v>
       </c>
-      <c r="E8" s="60" t="n">
-        <v>719</v>
-      </c>
-      <c r="F8" s="61" t="n">
+      <c r="E8" s="9" t="n">
+        <v>731</v>
+      </c>
+      <c r="F8" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>7</v>
@@ -1353,51 +1328,51 @@
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C9" s="54" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Insumos Facturación</t>
         </is>
       </c>
-      <c r="D9" s="60" t="n">
+      <c r="D9" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="E9" s="60" t="n">
-        <v>401</v>
-      </c>
-      <c r="F9" s="61" t="n">
+      <c r="E9" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.2301369863013699</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H9" s="17" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n"/>
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C10" s="54" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Automatización / Siigo</t>
         </is>
       </c>
-      <c r="D10" s="60" t="n">
+      <c r="D10" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E10" s="60" t="n">
+      <c r="E10" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="F10" s="61" t="n">
+      <c r="F10" s="10" t="n">
         <v>0.5726027397260274</v>
       </c>
       <c r="G10" s="11" t="n">
@@ -1408,7 +1383,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>CONCENTRACIÓN DE LA CARGA EN EL MES</t>
         </is>
@@ -1437,111 +1412,111 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Días 1 a 7</t>
         </is>
       </c>
-      <c r="C15" s="60" t="n">
-        <v>63</v>
-      </c>
-      <c r="D15" s="61" t="n">
-        <v>0.2093023255813954</v>
-      </c>
-      <c r="E15" s="54" t="inlineStr">
+      <c r="C15" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>0.2036363636363636</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Apertura del mes y facturación</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Días 8 a 14</t>
         </is>
       </c>
-      <c r="C16" s="60" t="n">
-        <v>90</v>
+      <c r="C16" s="9" t="n">
+        <v>85</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.2990033222591362</v>
-      </c>
-      <c r="E16" s="54" t="inlineStr">
+        <v>0.3090909090909091</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Cierre contable e insumos del informe</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="55" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Días 15 a 21</t>
         </is>
       </c>
-      <c r="C17" s="60" t="n">
-        <v>54</v>
-      </c>
-      <c r="D17" s="61" t="n">
-        <v>0.1794019933554817</v>
-      </c>
-      <c r="E17" s="54" t="inlineStr">
+      <c r="C17" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>0.1709090909090909</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Entrega a Gerencia, socios y RADIAN</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Días 22 a 28</t>
         </is>
       </c>
-      <c r="C18" s="60" t="n">
-        <v>64</v>
-      </c>
-      <c r="D18" s="61" t="n">
-        <v>0.212624584717608</v>
-      </c>
-      <c r="E18" s="54" t="inlineStr">
+      <c r="C18" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.2181818181818182</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Causaciones y nómina de segunda quincena</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="55" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Días 29 al cierre</t>
         </is>
       </c>
-      <c r="C19" s="60" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" s="61" t="n">
-        <v>0.09966777408637874</v>
-      </c>
-      <c r="E19" s="54" t="inlineStr">
+      <c r="C19" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.09818181818181818</v>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Desembolsos y archivo plano</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="53" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C20" s="62" t="n">
-        <v>301</v>
-      </c>
-      <c r="D20" s="63" t="n">
+      <c r="C20" s="21" t="n">
+        <v>275</v>
+      </c>
+      <c r="D20" s="22" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="23" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="52" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>HALLAZGOS</t>
         </is>
@@ -1558,8 +1533,8 @@
           <t>El 30% de la carga del mes cae entre los días 8 y 14. Coincide con el cierre contable y con los cinco insumos del informe.</t>
         </is>
       </c>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="58" t="n"/>
+      <c r="D24" s="56" t="n"/>
+      <c r="E24" s="57" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="24" t="inlineStr">
@@ -1569,11 +1544,11 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>15 tareas simultáneas del equipo el día 10, 12, 13. Es el punto más tenso del ciclo.</t>
-        </is>
-      </c>
-      <c r="D25" s="57" t="n"/>
-      <c r="E25" s="58" t="n"/>
+          <t>14 tareas simultáneas del equipo el día 10, 12, 13. Es el punto más tenso del ciclo.</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="n"/>
+      <c r="E25" s="57" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="B26" s="24" t="inlineStr">
@@ -1586,8 +1561,8 @@
           <t>Pico de 7 tareas propias en un mismo día. Es la posición con la ventana más apretada del mes.</t>
         </is>
       </c>
-      <c r="D26" s="57" t="n"/>
-      <c r="E26" s="58" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="57" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="24" t="inlineStr">
@@ -1600,8 +1575,8 @@
           <t>Ocupación del 100%: tiene tareas abiertas todos los días del año por el registro diario de RC y RP.</t>
         </is>
       </c>
-      <c r="D27" s="57" t="n"/>
-      <c r="E27" s="58" t="n"/>
+      <c r="D27" s="56" t="n"/>
+      <c r="E27" s="57" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="B28" s="24" t="inlineStr">
@@ -1614,8 +1589,8 @@
           <t>Dos compromisos con fecha: definir viáticos de tarjeta (días 6 a 10) y dar feedback al informe (días 13 a 14).</t>
         </is>
       </c>
-      <c r="D28" s="57" t="n"/>
-      <c r="E28" s="58" t="n"/>
+      <c r="D28" s="56" t="n"/>
+      <c r="E28" s="57" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1676,7 +1651,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>DÍAS-TAREA POR MES</t>
         </is>
@@ -1796,7 +1771,7 @@
       <c r="N6" s="28" t="n">
         <v>102</v>
       </c>
-      <c r="O6" s="62" t="n">
+      <c r="O6" s="21" t="n">
         <v>1196</v>
       </c>
     </row>
@@ -1842,7 +1817,7 @@
       <c r="N7" s="28" t="n">
         <v>85</v>
       </c>
-      <c r="O7" s="62" t="n">
+      <c r="O7" s="21" t="n">
         <v>1003</v>
       </c>
     </row>
@@ -1853,43 +1828,43 @@
         </is>
       </c>
       <c r="C8" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>57</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>57</v>
+      </c>
+      <c r="I8" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <v>58</v>
+      </c>
+      <c r="K8" s="30" t="n">
         <v>64</v>
       </c>
-      <c r="D8" s="30" t="n">
-        <v>54</v>
-      </c>
-      <c r="E8" s="30" t="n">
+      <c r="L8" s="30" t="n">
+        <v>58</v>
+      </c>
+      <c r="M8" s="30" t="n">
         <v>64</v>
       </c>
-      <c r="F8" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <v>64</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="I8" s="30" t="n">
-        <v>64</v>
-      </c>
-      <c r="J8" s="30" t="n">
-        <v>57</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>63</v>
-      </c>
-      <c r="L8" s="30" t="n">
-        <v>57</v>
-      </c>
-      <c r="M8" s="30" t="n">
-        <v>63</v>
-      </c>
       <c r="N8" s="30" t="n">
-        <v>57</v>
-      </c>
-      <c r="O8" s="62" t="n">
-        <v>719</v>
+        <v>58</v>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>731</v>
       </c>
     </row>
     <row r="9">
@@ -1898,140 +1873,140 @@
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="G9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="I9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="J9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="K9" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="L9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="M9" s="33" t="n">
-        <v>33</v>
-      </c>
-      <c r="N9" s="33" t="n">
-        <v>34</v>
-      </c>
-      <c r="O9" s="62" t="n">
-        <v>401</v>
+      <c r="C9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" s="21" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Edgar</t>
         </is>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="D10" s="60" t="n">
+      <c r="D10" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="60" t="n">
+      <c r="E10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="F10" s="60" t="n">
+      <c r="F10" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="60" t="n">
+      <c r="G10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="H10" s="60" t="n">
+      <c r="H10" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="I10" s="60" t="n">
+      <c r="I10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="J10" s="60" t="n">
+      <c r="J10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="K10" s="60" t="n">
+      <c r="K10" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="L10" s="60" t="n">
+      <c r="L10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="M10" s="60" t="n">
+      <c r="M10" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="N10" s="60" t="n">
+      <c r="N10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="O10" s="62" t="n">
+      <c r="O10" s="21" t="n">
         <v>269</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>EQUIPO</t>
         </is>
       </c>
-      <c r="C11" s="62" t="n">
-        <v>308</v>
-      </c>
-      <c r="D11" s="62" t="n">
-        <v>271</v>
-      </c>
-      <c r="E11" s="62" t="n">
-        <v>308</v>
-      </c>
-      <c r="F11" s="62" t="n">
-        <v>292</v>
-      </c>
-      <c r="G11" s="62" t="n">
-        <v>308</v>
-      </c>
-      <c r="H11" s="62" t="n">
-        <v>292</v>
-      </c>
-      <c r="I11" s="62" t="n">
-        <v>308</v>
-      </c>
-      <c r="J11" s="62" t="n">
-        <v>301</v>
-      </c>
-      <c r="K11" s="62" t="n">
-        <v>299</v>
-      </c>
-      <c r="L11" s="62" t="n">
-        <v>301</v>
-      </c>
-      <c r="M11" s="62" t="n">
-        <v>299</v>
-      </c>
-      <c r="N11" s="62" t="n">
-        <v>301</v>
-      </c>
-      <c r="O11" s="62" t="n">
-        <v>3588</v>
+      <c r="C11" s="21" t="n">
+        <v>282</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>248</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>282</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>267</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>282</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>267</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>282</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>275</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>274</v>
+      </c>
+      <c r="L11" s="21" t="n">
+        <v>275</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>274</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>275</v>
+      </c>
+      <c r="O11" s="21" t="n">
+        <v>3283</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="52" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>OCUPACIÓN Y PICO POR PERSONA</t>
         </is>
@@ -2080,159 +2055,159 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C16" s="60" t="n">
+      <c r="C16" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="60" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E16" s="61" t="n">
+      <c r="E16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>3.29</v>
       </c>
-      <c r="G16" s="36" t="n">
+      <c r="G16" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="37" t="inlineStr">
+      <c r="H16" s="36" t="inlineStr">
         <is>
           <t>14, 15</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="55" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C17" s="60" t="n">
+      <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E17" s="61" t="n">
+      <c r="E17" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>2.74</v>
       </c>
-      <c r="G17" s="36" t="n">
+      <c r="G17" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="37" t="inlineStr">
+      <c r="H17" s="36" t="inlineStr">
         <is>
           <t>10, 25, 26, 27, 28, 29</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="55" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C18" s="60" t="n">
+      <c r="C18" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>31 de 31</t>
         </is>
       </c>
-      <c r="E18" s="61" t="n">
+      <c r="E18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G18" s="38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G18" s="37" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="37" t="inlineStr">
+      <c r="H18" s="36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="55" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C19" s="60" t="n">
+      <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="60" t="inlineStr">
-        <is>
-          <t>31 de 31</t>
-        </is>
-      </c>
-      <c r="E19" s="61" t="n">
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>7 de 31</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G19" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G19" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="37" t="inlineStr">
-        <is>
-          <t>10, 11, 12</t>
+      <c r="H19" s="36" t="inlineStr">
+        <is>
+          <t>9, 10, 11, 12, 26, 27…</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C20" s="60" t="n">
+      <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>18 de 31</t>
         </is>
       </c>
-      <c r="E20" s="61" t="n">
+      <c r="E20" s="10" t="n">
         <v>0.5806451612903226</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>0.74</v>
       </c>
-      <c r="G20" s="39" t="n">
+      <c r="G20" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="37" t="inlineStr">
+      <c r="H20" s="36" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="64" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>Días-tarea: suma de los días que cada tarea permanece abierta. Mide exposición, no horas trabajadas.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="64" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>Pico: máximo de tareas de esa persona abiertas en un mismo día. Verde hasta 3, ámbar 4 y 5, rojo desde 6.</t>
         </is>
@@ -2290,7 +2265,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="67" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>RESUMEN ANUAL</t>
         </is>
@@ -2333,21 +2308,21 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="68" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C6" s="69" t="n">
+      <c r="C6" s="58" t="n">
         <v>4.58</v>
       </c>
-      <c r="D6" s="70" t="n">
+      <c r="D6" s="59" t="n">
         <v>365</v>
       </c>
-      <c r="E6" s="71" t="n">
+      <c r="E6" s="60" t="n">
         <v>77</v>
       </c>
-      <c r="F6" s="71" t="n">
+      <c r="F6" s="60" t="n">
         <v>104</v>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -2357,21 +2332,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="68" t="inlineStr">
+      <c r="B7" s="54" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C7" s="69" t="n">
+      <c r="C7" s="58" t="n">
         <v>3.84</v>
       </c>
-      <c r="D7" s="72" t="n">
+      <c r="D7" s="61" t="n">
         <v>202</v>
       </c>
-      <c r="E7" s="71" t="n">
+      <c r="E7" s="60" t="n">
         <v>71</v>
       </c>
-      <c r="F7" s="71" t="n">
+      <c r="F7" s="60" t="n">
         <v>104</v>
       </c>
       <c r="G7" s="25" t="inlineStr">
@@ -2381,21 +2356,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="68" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C8" s="73" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="D8" s="72" t="n">
-        <v>72</v>
-      </c>
-      <c r="E8" s="71" t="n">
+      <c r="C8" s="62" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D8" s="61" t="n">
+        <v>84</v>
+      </c>
+      <c r="E8" s="60" t="n">
         <v>48</v>
       </c>
-      <c r="F8" s="71" t="n">
+      <c r="F8" s="60" t="n">
         <v>104</v>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -2405,45 +2380,45 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C9" s="74" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="D9" s="72" t="n">
+      <c r="C9" s="63" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D9" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="71" t="n">
+      <c r="E9" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="71" t="n">
-        <v>104</v>
+      <c r="F9" s="60" t="n">
+        <v>24</v>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>Carga continua de baja simultaneidad</t>
+          <t>Interviene en dos momentos puntuales del mes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="68" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C10" s="74" t="n">
+      <c r="C10" s="63" t="n">
         <v>1.03</v>
       </c>
-      <c r="D10" s="72" t="n">
+      <c r="D10" s="61" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="71" t="n">
+      <c r="E10" s="60" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="71" t="n">
+      <c r="F10" s="60" t="n">
         <v>59</v>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -2453,7 +2428,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="67" t="inlineStr">
+      <c r="B13" s="51" t="inlineStr">
         <is>
           <t>FRENTES ABIERTOS POR DÍA HÁBIL, MES A MES</t>
         </is>
@@ -2532,329 +2507,329 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="68" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>Isnardi</t>
         </is>
       </c>
-      <c r="C15" s="75" t="n">
+      <c r="C15" s="64" t="n">
         <v>4.64</v>
       </c>
-      <c r="D15" s="75" t="n">
+      <c r="D15" s="64" t="n">
         <v>4.5</v>
       </c>
-      <c r="E15" s="75" t="n">
+      <c r="E15" s="64" t="n">
         <v>4.64</v>
       </c>
-      <c r="F15" s="75" t="n">
+      <c r="F15" s="64" t="n">
         <v>4.45</v>
       </c>
-      <c r="G15" s="75" t="n">
+      <c r="G15" s="64" t="n">
         <v>4.86</v>
       </c>
-      <c r="H15" s="75" t="n">
+      <c r="H15" s="64" t="n">
         <v>4.45</v>
       </c>
-      <c r="I15" s="75" t="n">
+      <c r="I15" s="64" t="n">
         <v>4.43</v>
       </c>
-      <c r="J15" s="75" t="n">
+      <c r="J15" s="64" t="n">
         <v>4.86</v>
       </c>
-      <c r="K15" s="75" t="n">
+      <c r="K15" s="64" t="n">
         <v>4.45</v>
       </c>
-      <c r="L15" s="75" t="n">
+      <c r="L15" s="64" t="n">
         <v>4.64</v>
       </c>
-      <c r="M15" s="75" t="n">
+      <c r="M15" s="64" t="n">
         <v>4.67</v>
       </c>
-      <c r="N15" s="75" t="n">
+      <c r="N15" s="64" t="n">
         <v>4.43</v>
       </c>
-      <c r="O15" s="76" t="n">
+      <c r="O15" s="65" t="n">
         <v>4.58</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="68" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="C16" s="75" t="n">
+      <c r="C16" s="64" t="n">
         <v>3.86</v>
       </c>
-      <c r="D16" s="75" t="n">
+      <c r="D16" s="64" t="n">
         <v>3.8</v>
       </c>
-      <c r="E16" s="75" t="n">
+      <c r="E16" s="64" t="n">
         <v>3.86</v>
       </c>
-      <c r="F16" s="75" t="n">
+      <c r="F16" s="64" t="n">
         <v>3.77</v>
       </c>
-      <c r="G16" s="75" t="n">
+      <c r="G16" s="64" t="n">
         <v>4.05</v>
       </c>
-      <c r="H16" s="75" t="n">
+      <c r="H16" s="64" t="n">
         <v>3.77</v>
       </c>
-      <c r="I16" s="75" t="n">
+      <c r="I16" s="64" t="n">
         <v>3.7</v>
       </c>
-      <c r="J16" s="75" t="n">
+      <c r="J16" s="64" t="n">
         <v>4.05</v>
       </c>
-      <c r="K16" s="75" t="n">
+      <c r="K16" s="64" t="n">
         <v>3.77</v>
       </c>
-      <c r="L16" s="75" t="n">
+      <c r="L16" s="64" t="n">
         <v>3.86</v>
       </c>
-      <c r="M16" s="75" t="n">
+      <c r="M16" s="64" t="n">
         <v>3.95</v>
       </c>
-      <c r="N16" s="75" t="n">
+      <c r="N16" s="64" t="n">
         <v>3.7</v>
       </c>
-      <c r="O16" s="76" t="n">
+      <c r="O16" s="65" t="n">
         <v>3.84</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="68" t="inlineStr">
+      <c r="B17" s="54" t="inlineStr">
         <is>
           <t>Cristian</t>
         </is>
       </c>
-      <c r="C17" s="77" t="n">
+      <c r="C17" s="66" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D17" s="66" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E17" s="66" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F17" s="66" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G17" s="66" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H17" s="66" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I17" s="66" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J17" s="66" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K17" s="66" t="n">
         <v>2.91</v>
       </c>
-      <c r="D17" s="77" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E17" s="77" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="F17" s="77" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="G17" s="77" t="n">
+      <c r="L17" s="66" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M17" s="66" t="n">
         <v>3.05</v>
       </c>
-      <c r="H17" s="77" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="I17" s="77" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="J17" s="77" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K17" s="77" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="L17" s="77" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="M17" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" s="78" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O17" s="76" t="n">
-        <v>2.75</v>
+      <c r="N17" s="66" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O17" s="65" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="68" t="inlineStr">
+      <c r="B18" s="54" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C18" s="78" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="D18" s="78" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E18" s="78" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F18" s="78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G18" s="78" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H18" s="78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I18" s="78" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J18" s="78" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="K18" s="78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L18" s="78" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M18" s="78" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N18" s="78" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O18" s="76" t="n">
-        <v>1.54</v>
+      <c r="C18" s="67" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="D18" s="67" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E18" s="67" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F18" s="67" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G18" s="67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H18" s="67" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I18" s="67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J18" s="67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K18" s="67" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L18" s="67" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M18" s="67" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N18" s="67" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O18" s="65" t="n">
+        <v>0.32</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="68" t="inlineStr">
+      <c r="B19" s="54" t="inlineStr">
         <is>
           <t>Edgar</t>
         </is>
       </c>
-      <c r="C19" s="78" t="n">
+      <c r="C19" s="67" t="n">
         <v>1.05</v>
       </c>
-      <c r="D19" s="78" t="n">
+      <c r="D19" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="78" t="n">
+      <c r="E19" s="67" t="n">
         <v>1.05</v>
       </c>
-      <c r="F19" s="78" t="n">
+      <c r="F19" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="78" t="n">
+      <c r="G19" s="67" t="n">
         <v>1.1</v>
       </c>
-      <c r="H19" s="78" t="n">
+      <c r="H19" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="78" t="n">
+      <c r="I19" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="78" t="n">
+      <c r="J19" s="67" t="n">
         <v>1.1</v>
       </c>
-      <c r="K19" s="78" t="n">
+      <c r="K19" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="78" t="n">
+      <c r="L19" s="67" t="n">
         <v>1.05</v>
       </c>
-      <c r="M19" s="78" t="n">
+      <c r="M19" s="67" t="n">
         <v>1.05</v>
       </c>
-      <c r="N19" s="78" t="n">
+      <c r="N19" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="O19" s="76" t="n">
+      <c r="O19" s="65" t="n">
         <v>1.03</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="68" t="inlineStr">
         <is>
           <t>EQUIPO</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n">
-        <v>14</v>
-      </c>
-      <c r="D20" s="80" t="n">
-        <v>13.55</v>
-      </c>
-      <c r="E20" s="80" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" s="80" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="G20" s="80" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="H20" s="80" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="I20" s="80" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="J20" s="80" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="K20" s="80" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="L20" s="80" t="n">
-        <v>13.68</v>
-      </c>
-      <c r="M20" s="80" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="N20" s="80" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="O20" s="76" t="n">
-        <v>13.76</v>
+      <c r="C20" s="69" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="D20" s="69" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E20" s="69" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="F20" s="69" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="G20" s="69" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="H20" s="69" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="I20" s="69" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="J20" s="69" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K20" s="69" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="L20" s="69" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M20" s="69" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="N20" s="69" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="O20" s="65" t="n">
+        <v>12.59</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="81" t="inlineStr">
+      <c r="B21" s="70" t="inlineStr">
         <is>
           <t>Días hábiles</t>
         </is>
       </c>
-      <c r="C21" s="82" t="n">
+      <c r="C21" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="D21" s="82" t="n">
+      <c r="D21" s="71" t="n">
         <v>20</v>
       </c>
-      <c r="E21" s="82" t="n">
+      <c r="E21" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="F21" s="82" t="n">
+      <c r="F21" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="G21" s="82" t="n">
+      <c r="G21" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="H21" s="82" t="n">
+      <c r="H21" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="I21" s="82" t="n">
+      <c r="I21" s="71" t="n">
         <v>23</v>
       </c>
-      <c r="J21" s="82" t="n">
+      <c r="J21" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="K21" s="82" t="n">
+      <c r="K21" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="L21" s="82" t="n">
+      <c r="L21" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="M21" s="82" t="n">
+      <c r="M21" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="N21" s="82" t="n">
+      <c r="N21" s="71" t="n">
         <v>23</v>
       </c>
-      <c r="O21" s="83" t="n">
+      <c r="O21" s="72" t="n">
         <v>261</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="67" t="inlineStr">
+      <c r="B23" s="51" t="inlineStr">
         <is>
           <t>DÍAS DEL MES CON 3 O MÁS FRENTES ABIERTOS</t>
         </is>
@@ -2933,208 +2908,208 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="68" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
         <is>
           <t>Isnardi</t>
         </is>
       </c>
-      <c r="C25" s="70" t="n">
+      <c r="C25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="D25" s="70" t="n">
+      <c r="D25" s="59" t="n">
         <v>28</v>
       </c>
-      <c r="E25" s="70" t="n">
+      <c r="E25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="F25" s="70" t="n">
+      <c r="F25" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="G25" s="70" t="n">
+      <c r="G25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="H25" s="70" t="n">
+      <c r="H25" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="I25" s="70" t="n">
+      <c r="I25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="J25" s="70" t="n">
+      <c r="J25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="K25" s="70" t="n">
+      <c r="K25" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="L25" s="70" t="n">
+      <c r="L25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="M25" s="70" t="n">
+      <c r="M25" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="N25" s="70" t="n">
+      <c r="N25" s="59" t="n">
         <v>31</v>
       </c>
-      <c r="O25" s="84" t="n">
+      <c r="O25" s="73" t="n">
         <v>365</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="68" t="inlineStr">
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="C26" s="85" t="n">
+      <c r="C26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="D26" s="85" t="n">
+      <c r="D26" s="74" t="n">
         <v>15</v>
       </c>
-      <c r="E26" s="85" t="n">
+      <c r="E26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="F26" s="85" t="n">
+      <c r="F26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="85" t="n">
+      <c r="G26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="H26" s="85" t="n">
+      <c r="H26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="I26" s="85" t="n">
+      <c r="I26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="J26" s="85" t="n">
+      <c r="J26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="K26" s="85" t="n">
+      <c r="K26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="L26" s="85" t="n">
+      <c r="L26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="M26" s="85" t="n">
+      <c r="M26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="N26" s="85" t="n">
+      <c r="N26" s="74" t="n">
         <v>17</v>
       </c>
-      <c r="O26" s="84" t="n">
+      <c r="O26" s="73" t="n">
         <v>202</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="68" t="inlineStr">
+      <c r="B27" s="54" t="inlineStr">
         <is>
           <t>Cristian</t>
         </is>
       </c>
-      <c r="C27" s="71" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="71" t="n">
-        <v>7</v>
-      </c>
-      <c r="F27" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="G27" s="71" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" s="71" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="K27" s="71" t="n">
-        <v>7</v>
-      </c>
-      <c r="L27" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="M27" s="71" t="n">
-        <v>7</v>
-      </c>
-      <c r="N27" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" s="84" t="n">
-        <v>72</v>
+      <c r="C27" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="N27" s="60" t="n">
+        <v>6</v>
+      </c>
+      <c r="O27" s="73" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="86" t="inlineStr">
+      <c r="B30" s="75" t="inlineStr">
         <is>
           <t>HALLAZGO</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="87" t="inlineStr">
-        <is>
-          <t>·  Tesorería registra 3 o más frentes abiertos los 365 días del año, incluidos los 104 días de fin de semana.</t>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>·  Tesorería registra 3 o más frentes abiertos 365 de los 365 días del año, incluidos los 104 días de fin de semana.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="87" t="inlineStr">
+      <c r="B32" s="55" t="inlineStr">
         <is>
           <t>·  No existe un solo día del calendario en que Tesorería opere con menos de tres asuntos simultáneos.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="87" t="inlineStr">
-        <is>
-          <t>·  El Auxiliar Contable está en esa condición 202 días al año; Contaduría 72 días, de ellos 48 con cuatro o más.</t>
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t>·  El Auxiliar Contable está en esa condición 202 días al año; Contaduría 84 días, de ellos 48 con cuatro o más.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="87" t="inlineStr">
-        <is>
-          <t>·  El equipo sostiene entre 13 y 15 frentes por día hábil todos los meses: la diferencia entre el mes más y menos cargado no llega al 12%.</t>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>·  El equipo sostiene entre 12 y 13 frentes por día hábil todos los meses: no hay temporada baja.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="67" t="inlineStr">
+      <c r="B36" s="51" t="inlineStr">
         <is>
           <t>QUÉ MIDE Y QUÉ NO</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="88" t="inlineStr">
+      <c r="B37" s="76" t="inlineStr">
         <is>
           <t>·  Mide simultaneidad: cuántos asuntos distintos permanecen abiertos a la vez, con su costo de atención y cambio de contexto.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="88" t="inlineStr">
+      <c r="B38" s="76" t="inlineStr">
         <is>
           <t>·  NO mide horas trabajadas. Para cuantificar horas se requiere registro de tiempos.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="88" t="inlineStr">
+      <c r="B39" s="76" t="inlineStr">
         <is>
           <t>·  Días hábiles contados de lunes a viernes, sin descontar festivos. El cálculo es conservador.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="88" t="inlineStr">
+      <c r="B40" s="76" t="inlineStr">
         <is>
           <t>·  Semáforo: verde por debajo de 2,5 frentes · ámbar entre 2,5 y 3,5 · rojo desde 3,5.</t>
         </is>
@@ -3220,12 +3195,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>1 al 5</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
@@ -3235,24 +3210,24 @@
           <t>Emisión de facturas electrónicas</t>
         </is>
       </c>
-      <c r="E5" s="60" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Día 5</t>
         </is>
       </c>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="F5" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>3 al 9</t>
         </is>
       </c>
-      <c r="C6" s="54" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -3262,24 +3237,24 @@
           <t>Conciliación bancaria</t>
         </is>
       </c>
-      <c r="E6" s="60" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Día 9</t>
         </is>
       </c>
-      <c r="F6" s="43" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>6 al 10</t>
         </is>
       </c>
-      <c r="C7" s="54" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Luis + Edgar</t>
         </is>
@@ -3289,24 +3264,24 @@
           <t>Conciliación de tarjeta y definición de viáticos</t>
         </is>
       </c>
-      <c r="E7" s="60" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Día 10</t>
         </is>
       </c>
-      <c r="F7" s="42" t="inlineStr">
+      <c r="F7" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>10 al 13</t>
         </is>
       </c>
-      <c r="C8" s="54" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -3316,24 +3291,24 @@
           <t>Causación de seguridad social</t>
         </is>
       </c>
-      <c r="E8" s="60" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Día 13</t>
         </is>
       </c>
-      <c r="F8" s="44" t="inlineStr">
+      <c r="F8" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="40" t="inlineStr">
         <is>
           <t>10 al 14</t>
         </is>
       </c>
-      <c r="C9" s="54" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -3343,24 +3318,24 @@
           <t>Causación de nómina primera quincena</t>
         </is>
       </c>
-      <c r="E9" s="60" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Día 14</t>
         </is>
       </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="F9" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
         <is>
           <t>10 al 14</t>
         </is>
       </c>
-      <c r="C10" s="54" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -3370,24 +3345,24 @@
           <t>Cierre contable y retención en la fuente</t>
         </is>
       </c>
-      <c r="E10" s="60" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Día 14</t>
         </is>
       </c>
-      <c r="F10" s="44" t="inlineStr">
+      <c r="F10" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="40" t="inlineStr">
         <is>
           <t>9 al 13</t>
         </is>
       </c>
-      <c r="C11" s="54" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -3397,24 +3372,24 @@
           <t>Insumos del informe: flujo, cartera, recaudo, EESF, ER</t>
         </is>
       </c>
-      <c r="E11" s="60" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Día 13</t>
         </is>
       </c>
-      <c r="F11" s="42" t="inlineStr">
+      <c r="F11" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="40" t="inlineStr">
         <is>
           <t>10 al 12</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
@@ -3424,24 +3399,24 @@
           <t>Comentarios comerciales al informe</t>
         </is>
       </c>
-      <c r="E12" s="60" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Día 12</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F12" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>13 al 15</t>
         </is>
       </c>
-      <c r="C13" s="54" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
@@ -3451,24 +3426,24 @@
           <t>Pago de seguridad social</t>
         </is>
       </c>
-      <c r="E13" s="60" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Día 15</t>
         </is>
       </c>
-      <c r="F13" s="44" t="inlineStr">
+      <c r="F13" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="40" t="inlineStr">
         <is>
           <t>13 al 14</t>
         </is>
       </c>
-      <c r="C14" s="54" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
@@ -3478,24 +3453,24 @@
           <t>Feedback del informe antes de socios</t>
         </is>
       </c>
-      <c r="E14" s="60" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Día 14</t>
         </is>
       </c>
-      <c r="F14" s="42" t="inlineStr">
+      <c r="F14" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="40" t="inlineStr">
         <is>
           <t>14 al 16</t>
         </is>
       </c>
-      <c r="C15" s="54" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
@@ -3505,24 +3480,24 @@
           <t>Desembolso de nómina primera quincena</t>
         </is>
       </c>
-      <c r="E15" s="60" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Día 16</t>
         </is>
       </c>
-      <c r="F15" s="44" t="inlineStr">
+      <c r="F15" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="40" t="inlineStr">
         <is>
           <t>13 al 15</t>
         </is>
       </c>
-      <c r="C16" s="54" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -3532,24 +3507,24 @@
           <t>Entrega del dashboard a Gerencia</t>
         </is>
       </c>
-      <c r="E16" s="60" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Día 15</t>
         </is>
       </c>
-      <c r="F16" s="42" t="inlineStr">
+      <c r="F16" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>15 al 20</t>
         </is>
       </c>
-      <c r="C17" s="54" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -3559,24 +3534,24 @@
           <t>Proceso con socios</t>
         </is>
       </c>
-      <c r="E17" s="60" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Día 20</t>
         </is>
       </c>
-      <c r="F17" s="42" t="inlineStr">
+      <c r="F17" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="40" t="inlineStr">
         <is>
           <t>15 al 21</t>
         </is>
       </c>
-      <c r="C18" s="54" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
@@ -3586,24 +3561,24 @@
           <t>Declaración de IVA (meses del bimestre)</t>
         </is>
       </c>
-      <c r="E18" s="60" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Día 21</t>
         </is>
       </c>
-      <c r="F18" s="44" t="inlineStr">
+      <c r="F18" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>15 al 25</t>
         </is>
       </c>
-      <c r="C19" s="54" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -3613,24 +3588,24 @@
           <t>Validación RADIAN</t>
         </is>
       </c>
-      <c r="E19" s="60" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Día 25</t>
         </is>
       </c>
-      <c r="F19" s="43" t="inlineStr">
+      <c r="F19" s="42" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>25 al 29</t>
         </is>
       </c>
-      <c r="C20" s="54" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
@@ -3640,24 +3615,24 @@
           <t>Causación de nómina segunda quincena</t>
         </is>
       </c>
-      <c r="E20" s="60" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Día 29</t>
         </is>
       </c>
-      <c r="F20" s="44" t="inlineStr">
+      <c r="F20" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="40" t="inlineStr">
         <is>
           <t>26 al cierre</t>
         </is>
       </c>
-      <c r="C21" s="54" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Luis + Edgar</t>
         </is>
@@ -3667,24 +3642,24 @@
           <t>Archivo plano para facturar el día 1</t>
         </is>
       </c>
-      <c r="E21" s="60" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F21" s="42" t="inlineStr">
+      <c r="F21" s="41" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>29 al cierre</t>
         </is>
       </c>
-      <c r="C22" s="54" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
@@ -3694,33 +3669,33 @@
           <t>Desembolso de nómina segunda quincena</t>
         </is>
       </c>
-      <c r="E22" s="60" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Cierre</t>
         </is>
       </c>
-      <c r="F22" s="44" t="inlineStr">
+      <c r="F22" s="43" t="inlineStr">
         <is>
           <t>Legal</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="64" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Legal: tiene vencimiento de ley, no admite aplazamiento.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="64" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>Alta: si se retrasa, frena a otra persona del equipo.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="64" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>Media: afecta solo al proceso propio.</t>
         </is>
@@ -3769,1865 +3744,1878 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>CÓMO SE DILIGENCIA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="56" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>·  Al cierre de cada mes, tomar de la aplicación el número de tareas completadas por persona.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="56" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>·  Escribir ese número en las celdas de fondo amarillo. Las demás columnas se calculan solas.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="56" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>·  La columna Programadas ya viene con el dato del mes correspondiente.</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>ENERO</t>
         </is>
       </c>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="46" t="n"/>
-      <c r="E9" s="46" t="n"/>
-      <c r="F9" s="46" t="n"/>
-      <c r="G9" s="46" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="45" t="n"/>
+      <c r="G9" s="45" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C10" s="47" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E10" s="47" t="inlineStr">
+      <c r="E10" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F10" s="47" t="inlineStr">
+      <c r="F10" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G10" s="47" t="inlineStr">
+      <c r="G10" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C11" s="60" t="n">
+      <c r="C11" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="48" t="n"/>
-      <c r="E11" s="61">
+      <c r="D11" s="47" t="n"/>
+      <c r="E11" s="10">
         <f>IFERROR(D11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="48" t="n"/>
+      <c r="F11" s="47" t="n"/>
       <c r="G11" s="25" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D12" s="48" t="n"/>
-      <c r="E12" s="61">
+      <c r="D12" s="47" t="n"/>
+      <c r="E12" s="10">
         <f>IFERROR(D12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="48" t="n"/>
+      <c r="F12" s="47" t="n"/>
       <c r="G12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C13" s="60" t="n">
+      <c r="C13" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D13" s="48" t="n"/>
-      <c r="E13" s="61">
+      <c r="D13" s="47" t="n"/>
+      <c r="E13" s="10">
         <f>IFERROR(D13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="48" t="n"/>
+      <c r="F13" s="47" t="n"/>
       <c r="G13" s="25" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C14" s="60" t="n">
+      <c r="C14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="48" t="n"/>
-      <c r="E14" s="61">
+      <c r="D14" s="47" t="n"/>
+      <c r="E14" s="10">
         <f>IFERROR(D14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="48" t="n"/>
+      <c r="F14" s="47" t="n"/>
       <c r="G14" s="25" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C15" s="60" t="n">
+      <c r="C15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="48" t="n"/>
-      <c r="E15" s="61">
+      <c r="D15" s="47" t="n"/>
+      <c r="E15" s="10">
         <f>IFERROR(D15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="48" t="n"/>
+      <c r="F15" s="47" t="n"/>
       <c r="G15" s="25" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="53" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C16" s="62">
+      <c r="C16" s="21">
         <f>SUM(C11:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="62">
+      <c r="D16" s="21">
         <f>SUM(D11:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="63">
+      <c r="E16" s="22">
         <f>IFERROR(D16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="62">
+      <c r="F16" s="21">
         <f>SUM(F11:F15)</f>
         <v/>
       </c>
       <c r="G16" s="23" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>FEBRERO</t>
         </is>
       </c>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="46" t="n"/>
-      <c r="F18" s="46" t="n"/>
-      <c r="G18" s="46" t="n"/>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="45" t="n"/>
+      <c r="G18" s="45" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="47" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C19" s="47" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D19" s="47" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E19" s="47" t="inlineStr">
+      <c r="E19" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F19" s="47" t="inlineStr">
+      <c r="F19" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G19" s="47" t="inlineStr">
+      <c r="G19" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C20" s="60" t="n">
+      <c r="C20" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D20" s="48" t="n"/>
-      <c r="E20" s="61">
+      <c r="D20" s="47" t="n"/>
+      <c r="E20" s="10">
         <f>IFERROR(D20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="48" t="n"/>
+      <c r="F20" s="47" t="n"/>
       <c r="G20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="55" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C21" s="60" t="n">
+      <c r="C21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="48" t="n"/>
-      <c r="E21" s="61">
+      <c r="D21" s="47" t="n"/>
+      <c r="E21" s="10">
         <f>IFERROR(D21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="48" t="n"/>
+      <c r="F21" s="47" t="n"/>
       <c r="G21" s="25" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="55" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C22" s="60" t="n">
+      <c r="C22" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D22" s="48" t="n"/>
-      <c r="E22" s="61">
+      <c r="D22" s="47" t="n"/>
+      <c r="E22" s="10">
         <f>IFERROR(D22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="48" t="n"/>
+      <c r="F22" s="47" t="n"/>
       <c r="G22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="55" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C23" s="60" t="n">
+      <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="48" t="n"/>
-      <c r="E23" s="61">
+      <c r="D23" s="47" t="n"/>
+      <c r="E23" s="10">
         <f>IFERROR(D23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="48" t="n"/>
+      <c r="F23" s="47" t="n"/>
       <c r="G23" s="25" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="55" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C24" s="60" t="n">
+      <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="48" t="n"/>
-      <c r="E24" s="61">
+      <c r="D24" s="47" t="n"/>
+      <c r="E24" s="10">
         <f>IFERROR(D24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="48" t="n"/>
+      <c r="F24" s="47" t="n"/>
       <c r="G24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C25" s="62">
+      <c r="C25" s="21">
         <f>SUM(C20:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="62">
+      <c r="D25" s="21">
         <f>SUM(D20:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="63">
+      <c r="E25" s="22">
         <f>IFERROR(D25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="62">
+      <c r="F25" s="21">
         <f>SUM(F20:F24)</f>
         <v/>
       </c>
       <c r="G25" s="23" t="inlineStr"/>
     </row>
+    <row r="26"/>
     <row r="27">
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="34" t="inlineStr">
         <is>
           <t>MARZO</t>
         </is>
       </c>
-      <c r="C27" s="46" t="n"/>
-      <c r="D27" s="46" t="n"/>
-      <c r="E27" s="46" t="n"/>
-      <c r="F27" s="46" t="n"/>
-      <c r="G27" s="46" t="n"/>
+      <c r="C27" s="45" t="n"/>
+      <c r="D27" s="45" t="n"/>
+      <c r="E27" s="45" t="n"/>
+      <c r="F27" s="45" t="n"/>
+      <c r="G27" s="45" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="47" t="inlineStr">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C28" s="47" t="inlineStr">
+      <c r="C28" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D28" s="47" t="inlineStr">
+      <c r="D28" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E28" s="47" t="inlineStr">
+      <c r="E28" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F28" s="47" t="inlineStr">
+      <c r="F28" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G28" s="47" t="inlineStr">
+      <c r="G28" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="55" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C29" s="60" t="n">
+      <c r="C29" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D29" s="48" t="n"/>
-      <c r="E29" s="61">
+      <c r="D29" s="47" t="n"/>
+      <c r="E29" s="10">
         <f>IFERROR(D29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="48" t="n"/>
+      <c r="F29" s="47" t="n"/>
       <c r="G29" s="25" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="55" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C30" s="60" t="n">
+      <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="48" t="n"/>
-      <c r="E30" s="61">
+      <c r="D30" s="47" t="n"/>
+      <c r="E30" s="10">
         <f>IFERROR(D30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="48" t="n"/>
+      <c r="F30" s="47" t="n"/>
       <c r="G30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="55" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C31" s="60" t="n">
+      <c r="C31" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D31" s="48" t="n"/>
-      <c r="E31" s="61">
+      <c r="D31" s="47" t="n"/>
+      <c r="E31" s="10">
         <f>IFERROR(D31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="48" t="n"/>
+      <c r="F31" s="47" t="n"/>
       <c r="G31" s="25" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="55" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C32" s="60" t="n">
+      <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="48" t="n"/>
-      <c r="E32" s="61">
+      <c r="D32" s="47" t="n"/>
+      <c r="E32" s="10">
         <f>IFERROR(D32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="48" t="n"/>
+      <c r="F32" s="47" t="n"/>
       <c r="G32" s="25" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="55" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C33" s="60" t="n">
+      <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="48" t="n"/>
-      <c r="E33" s="61">
+      <c r="D33" s="47" t="n"/>
+      <c r="E33" s="10">
         <f>IFERROR(D33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="48" t="n"/>
+      <c r="F33" s="47" t="n"/>
       <c r="G33" s="25" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="53" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C34" s="62">
+      <c r="C34" s="21">
         <f>SUM(C29:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="62">
+      <c r="D34" s="21">
         <f>SUM(D29:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="63">
+      <c r="E34" s="22">
         <f>IFERROR(D34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="62">
+      <c r="F34" s="21">
         <f>SUM(F29:F33)</f>
         <v/>
       </c>
       <c r="G34" s="23" t="inlineStr"/>
     </row>
+    <row r="35"/>
     <row r="36">
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>ABRIL</t>
         </is>
       </c>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="46" t="n"/>
-      <c r="F36" s="46" t="n"/>
-      <c r="G36" s="46" t="n"/>
+      <c r="C36" s="45" t="n"/>
+      <c r="D36" s="45" t="n"/>
+      <c r="E36" s="45" t="n"/>
+      <c r="F36" s="45" t="n"/>
+      <c r="G36" s="45" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="47" t="inlineStr">
+      <c r="B37" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C37" s="47" t="inlineStr">
+      <c r="C37" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D37" s="47" t="inlineStr">
+      <c r="D37" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E37" s="47" t="inlineStr">
+      <c r="E37" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F37" s="47" t="inlineStr">
+      <c r="F37" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G37" s="47" t="inlineStr">
+      <c r="G37" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="55" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C38" s="60" t="n">
+      <c r="C38" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="48" t="n"/>
-      <c r="E38" s="61">
+      <c r="D38" s="47" t="n"/>
+      <c r="E38" s="10">
         <f>IFERROR(D38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="48" t="n"/>
+      <c r="F38" s="47" t="n"/>
       <c r="G38" s="25" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="55" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C39" s="60" t="n">
+      <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="48" t="n"/>
-      <c r="E39" s="61">
+      <c r="D39" s="47" t="n"/>
+      <c r="E39" s="10">
         <f>IFERROR(D39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="48" t="n"/>
+      <c r="F39" s="47" t="n"/>
       <c r="G39" s="25" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="55" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C40" s="60" t="n">
+      <c r="C40" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D40" s="48" t="n"/>
-      <c r="E40" s="61">
+      <c r="D40" s="47" t="n"/>
+      <c r="E40" s="10">
         <f>IFERROR(D40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="48" t="n"/>
+      <c r="F40" s="47" t="n"/>
       <c r="G40" s="25" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="55" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C41" s="60" t="n">
+      <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="48" t="n"/>
-      <c r="E41" s="61">
+      <c r="D41" s="47" t="n"/>
+      <c r="E41" s="10">
         <f>IFERROR(D41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="48" t="n"/>
+      <c r="F41" s="47" t="n"/>
       <c r="G41" s="25" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="55" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C42" s="60" t="n">
+      <c r="C42" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="48" t="n"/>
-      <c r="E42" s="61">
+      <c r="D42" s="47" t="n"/>
+      <c r="E42" s="10">
         <f>IFERROR(D42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="48" t="n"/>
+      <c r="F42" s="47" t="n"/>
       <c r="G42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="53" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C43" s="62">
+      <c r="C43" s="21">
         <f>SUM(C38:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="21">
         <f>SUM(D38:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="63">
+      <c r="E43" s="22">
         <f>IFERROR(D43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="62">
+      <c r="F43" s="21">
         <f>SUM(F38:F42)</f>
         <v/>
       </c>
       <c r="G43" s="23" t="inlineStr"/>
     </row>
+    <row r="44"/>
     <row r="45">
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B45" s="34" t="inlineStr">
         <is>
           <t>MAYO</t>
         </is>
       </c>
-      <c r="C45" s="46" t="n"/>
-      <c r="D45" s="46" t="n"/>
-      <c r="E45" s="46" t="n"/>
-      <c r="F45" s="46" t="n"/>
-      <c r="G45" s="46" t="n"/>
+      <c r="C45" s="45" t="n"/>
+      <c r="D45" s="45" t="n"/>
+      <c r="E45" s="45" t="n"/>
+      <c r="F45" s="45" t="n"/>
+      <c r="G45" s="45" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="47" t="inlineStr">
+      <c r="B46" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C46" s="47" t="inlineStr">
+      <c r="C46" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D46" s="47" t="inlineStr">
+      <c r="D46" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E46" s="47" t="inlineStr">
+      <c r="E46" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F46" s="47" t="inlineStr">
+      <c r="F46" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G46" s="47" t="inlineStr">
+      <c r="G46" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="55" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C47" s="60" t="n">
+      <c r="C47" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D47" s="48" t="n"/>
-      <c r="E47" s="61">
+      <c r="D47" s="47" t="n"/>
+      <c r="E47" s="10">
         <f>IFERROR(D47/C47,"")</f>
         <v/>
       </c>
-      <c r="F47" s="48" t="n"/>
+      <c r="F47" s="47" t="n"/>
       <c r="G47" s="25" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="55" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C48" s="60" t="n">
+      <c r="C48" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D48" s="48" t="n"/>
-      <c r="E48" s="61">
+      <c r="D48" s="47" t="n"/>
+      <c r="E48" s="10">
         <f>IFERROR(D48/C48,"")</f>
         <v/>
       </c>
-      <c r="F48" s="48" t="n"/>
+      <c r="F48" s="47" t="n"/>
       <c r="G48" s="25" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="55" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C49" s="60" t="n">
+      <c r="C49" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D49" s="48" t="n"/>
-      <c r="E49" s="61">
+      <c r="D49" s="47" t="n"/>
+      <c r="E49" s="10">
         <f>IFERROR(D49/C49,"")</f>
         <v/>
       </c>
-      <c r="F49" s="48" t="n"/>
+      <c r="F49" s="47" t="n"/>
       <c r="G49" s="25" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="55" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C50" s="60" t="n">
+      <c r="C50" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="48" t="n"/>
-      <c r="E50" s="61">
+      <c r="D50" s="47" t="n"/>
+      <c r="E50" s="10">
         <f>IFERROR(D50/C50,"")</f>
         <v/>
       </c>
-      <c r="F50" s="48" t="n"/>
+      <c r="F50" s="47" t="n"/>
       <c r="G50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="55" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C51" s="60" t="n">
+      <c r="C51" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D51" s="48" t="n"/>
-      <c r="E51" s="61">
+      <c r="D51" s="47" t="n"/>
+      <c r="E51" s="10">
         <f>IFERROR(D51/C51,"")</f>
         <v/>
       </c>
-      <c r="F51" s="48" t="n"/>
+      <c r="F51" s="47" t="n"/>
       <c r="G51" s="25" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="53" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C52" s="62">
+      <c r="C52" s="21">
         <f>SUM(C47:C51)</f>
         <v/>
       </c>
-      <c r="D52" s="62">
+      <c r="D52" s="21">
         <f>SUM(D47:D51)</f>
         <v/>
       </c>
-      <c r="E52" s="63">
+      <c r="E52" s="22">
         <f>IFERROR(D52/C52,"")</f>
         <v/>
       </c>
-      <c r="F52" s="62">
+      <c r="F52" s="21">
         <f>SUM(F47:F51)</f>
         <v/>
       </c>
       <c r="G52" s="23" t="inlineStr"/>
     </row>
+    <row r="53"/>
     <row r="54">
-      <c r="B54" s="35" t="inlineStr">
+      <c r="B54" s="34" t="inlineStr">
         <is>
           <t>JUNIO</t>
         </is>
       </c>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
-      <c r="E54" s="46" t="n"/>
-      <c r="F54" s="46" t="n"/>
-      <c r="G54" s="46" t="n"/>
+      <c r="C54" s="45" t="n"/>
+      <c r="D54" s="45" t="n"/>
+      <c r="E54" s="45" t="n"/>
+      <c r="F54" s="45" t="n"/>
+      <c r="G54" s="45" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="47" t="inlineStr">
+      <c r="B55" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C55" s="47" t="inlineStr">
+      <c r="C55" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D55" s="47" t="inlineStr">
+      <c r="D55" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E55" s="47" t="inlineStr">
+      <c r="E55" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F55" s="47" t="inlineStr">
+      <c r="F55" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G55" s="47" t="inlineStr">
+      <c r="G55" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="55" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C56" s="60" t="n">
+      <c r="C56" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D56" s="48" t="n"/>
-      <c r="E56" s="61">
+      <c r="D56" s="47" t="n"/>
+      <c r="E56" s="10">
         <f>IFERROR(D56/C56,"")</f>
         <v/>
       </c>
-      <c r="F56" s="48" t="n"/>
+      <c r="F56" s="47" t="n"/>
       <c r="G56" s="25" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" s="55" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C57" s="60" t="n">
+      <c r="C57" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="61">
+      <c r="D57" s="47" t="n"/>
+      <c r="E57" s="10">
         <f>IFERROR(D57/C57,"")</f>
         <v/>
       </c>
-      <c r="F57" s="48" t="n"/>
+      <c r="F57" s="47" t="n"/>
       <c r="G57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="55" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C58" s="60" t="n">
+      <c r="C58" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D58" s="48" t="n"/>
-      <c r="E58" s="61">
+      <c r="D58" s="47" t="n"/>
+      <c r="E58" s="10">
         <f>IFERROR(D58/C58,"")</f>
         <v/>
       </c>
-      <c r="F58" s="48" t="n"/>
+      <c r="F58" s="47" t="n"/>
       <c r="G58" s="25" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" s="55" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C59" s="60" t="n">
+      <c r="C59" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D59" s="48" t="n"/>
-      <c r="E59" s="61">
+      <c r="D59" s="47" t="n"/>
+      <c r="E59" s="10">
         <f>IFERROR(D59/C59,"")</f>
         <v/>
       </c>
-      <c r="F59" s="48" t="n"/>
+      <c r="F59" s="47" t="n"/>
       <c r="G59" s="25" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="55" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C60" s="60" t="n">
+      <c r="C60" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D60" s="48" t="n"/>
-      <c r="E60" s="61">
+      <c r="D60" s="47" t="n"/>
+      <c r="E60" s="10">
         <f>IFERROR(D60/C60,"")</f>
         <v/>
       </c>
-      <c r="F60" s="48" t="n"/>
+      <c r="F60" s="47" t="n"/>
       <c r="G60" s="25" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" s="53" t="inlineStr">
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C61" s="62">
+      <c r="C61" s="21">
         <f>SUM(C56:C60)</f>
         <v/>
       </c>
-      <c r="D61" s="62">
+      <c r="D61" s="21">
         <f>SUM(D56:D60)</f>
         <v/>
       </c>
-      <c r="E61" s="63">
+      <c r="E61" s="22">
         <f>IFERROR(D61/C61,"")</f>
         <v/>
       </c>
-      <c r="F61" s="62">
+      <c r="F61" s="21">
         <f>SUM(F56:F60)</f>
         <v/>
       </c>
       <c r="G61" s="23" t="inlineStr"/>
     </row>
+    <row r="62"/>
     <row r="63">
-      <c r="B63" s="35" t="inlineStr">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>JULIO</t>
         </is>
       </c>
-      <c r="C63" s="46" t="n"/>
-      <c r="D63" s="46" t="n"/>
-      <c r="E63" s="46" t="n"/>
-      <c r="F63" s="46" t="n"/>
-      <c r="G63" s="46" t="n"/>
+      <c r="C63" s="45" t="n"/>
+      <c r="D63" s="45" t="n"/>
+      <c r="E63" s="45" t="n"/>
+      <c r="F63" s="45" t="n"/>
+      <c r="G63" s="45" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" s="47" t="inlineStr">
+      <c r="B64" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C64" s="47" t="inlineStr">
+      <c r="C64" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D64" s="47" t="inlineStr">
+      <c r="D64" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E64" s="47" t="inlineStr">
+      <c r="E64" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F64" s="47" t="inlineStr">
+      <c r="F64" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G64" s="47" t="inlineStr">
+      <c r="G64" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="55" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C65" s="60" t="n">
+      <c r="C65" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D65" s="48" t="n"/>
-      <c r="E65" s="61">
+      <c r="D65" s="47" t="n"/>
+      <c r="E65" s="10">
         <f>IFERROR(D65/C65,"")</f>
         <v/>
       </c>
-      <c r="F65" s="48" t="n"/>
+      <c r="F65" s="47" t="n"/>
       <c r="G65" s="25" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="55" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C66" s="60" t="n">
+      <c r="C66" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D66" s="48" t="n"/>
-      <c r="E66" s="61">
+      <c r="D66" s="47" t="n"/>
+      <c r="E66" s="10">
         <f>IFERROR(D66/C66,"")</f>
         <v/>
       </c>
-      <c r="F66" s="48" t="n"/>
+      <c r="F66" s="47" t="n"/>
       <c r="G66" s="25" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="55" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C67" s="60" t="n">
+      <c r="C67" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D67" s="48" t="n"/>
-      <c r="E67" s="61">
+      <c r="D67" s="47" t="n"/>
+      <c r="E67" s="10">
         <f>IFERROR(D67/C67,"")</f>
         <v/>
       </c>
-      <c r="F67" s="48" t="n"/>
+      <c r="F67" s="47" t="n"/>
       <c r="G67" s="25" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="55" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C68" s="60" t="n">
+      <c r="C68" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D68" s="48" t="n"/>
-      <c r="E68" s="61">
+      <c r="D68" s="47" t="n"/>
+      <c r="E68" s="10">
         <f>IFERROR(D68/C68,"")</f>
         <v/>
       </c>
-      <c r="F68" s="48" t="n"/>
+      <c r="F68" s="47" t="n"/>
       <c r="G68" s="25" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="55" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C69" s="60" t="n">
+      <c r="C69" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D69" s="48" t="n"/>
-      <c r="E69" s="61">
+      <c r="D69" s="47" t="n"/>
+      <c r="E69" s="10">
         <f>IFERROR(D69/C69,"")</f>
         <v/>
       </c>
-      <c r="F69" s="48" t="n"/>
+      <c r="F69" s="47" t="n"/>
       <c r="G69" s="25" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="53" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C70" s="62">
+      <c r="C70" s="21">
         <f>SUM(C65:C69)</f>
         <v/>
       </c>
-      <c r="D70" s="62">
+      <c r="D70" s="21">
         <f>SUM(D65:D69)</f>
         <v/>
       </c>
-      <c r="E70" s="63">
+      <c r="E70" s="22">
         <f>IFERROR(D70/C70,"")</f>
         <v/>
       </c>
-      <c r="F70" s="62">
+      <c r="F70" s="21">
         <f>SUM(F65:F69)</f>
         <v/>
       </c>
       <c r="G70" s="23" t="inlineStr"/>
     </row>
+    <row r="71"/>
     <row r="72">
-      <c r="B72" s="35" t="inlineStr">
+      <c r="B72" s="34" t="inlineStr">
         <is>
           <t>AGOSTO</t>
         </is>
       </c>
-      <c r="C72" s="46" t="n"/>
-      <c r="D72" s="46" t="n"/>
-      <c r="E72" s="46" t="n"/>
-      <c r="F72" s="46" t="n"/>
-      <c r="G72" s="46" t="n"/>
+      <c r="C72" s="45" t="n"/>
+      <c r="D72" s="45" t="n"/>
+      <c r="E72" s="45" t="n"/>
+      <c r="F72" s="45" t="n"/>
+      <c r="G72" s="45" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="47" t="inlineStr">
+      <c r="B73" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C73" s="47" t="inlineStr">
+      <c r="C73" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D73" s="47" t="inlineStr">
+      <c r="D73" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E73" s="47" t="inlineStr">
+      <c r="E73" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F73" s="47" t="inlineStr">
+      <c r="F73" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G73" s="47" t="inlineStr">
+      <c r="G73" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="55" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C74" s="60" t="n">
+      <c r="C74" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D74" s="48" t="n"/>
-      <c r="E74" s="61">
+      <c r="D74" s="47" t="n"/>
+      <c r="E74" s="10">
         <f>IFERROR(D74/C74,"")</f>
         <v/>
       </c>
-      <c r="F74" s="48" t="n"/>
+      <c r="F74" s="47" t="n"/>
       <c r="G74" s="25" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="55" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C75" s="60" t="n">
+      <c r="C75" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D75" s="48" t="n"/>
-      <c r="E75" s="61">
+      <c r="D75" s="47" t="n"/>
+      <c r="E75" s="10">
         <f>IFERROR(D75/C75,"")</f>
         <v/>
       </c>
-      <c r="F75" s="48" t="n"/>
+      <c r="F75" s="47" t="n"/>
       <c r="G75" s="25" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" s="55" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C76" s="60" t="n">
+      <c r="C76" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D76" s="48" t="n"/>
-      <c r="E76" s="61">
+      <c r="D76" s="47" t="n"/>
+      <c r="E76" s="10">
         <f>IFERROR(D76/C76,"")</f>
         <v/>
       </c>
-      <c r="F76" s="48" t="n"/>
+      <c r="F76" s="47" t="n"/>
       <c r="G76" s="25" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="55" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C77" s="60" t="n">
+      <c r="C77" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D77" s="48" t="n"/>
-      <c r="E77" s="61">
+      <c r="D77" s="47" t="n"/>
+      <c r="E77" s="10">
         <f>IFERROR(D77/C77,"")</f>
         <v/>
       </c>
-      <c r="F77" s="48" t="n"/>
+      <c r="F77" s="47" t="n"/>
       <c r="G77" s="25" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="55" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C78" s="60" t="n">
+      <c r="C78" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D78" s="48" t="n"/>
-      <c r="E78" s="61">
+      <c r="D78" s="47" t="n"/>
+      <c r="E78" s="10">
         <f>IFERROR(D78/C78,"")</f>
         <v/>
       </c>
-      <c r="F78" s="48" t="n"/>
+      <c r="F78" s="47" t="n"/>
       <c r="G78" s="25" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" s="53" t="inlineStr">
+      <c r="B79" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C79" s="62">
+      <c r="C79" s="21">
         <f>SUM(C74:C78)</f>
         <v/>
       </c>
-      <c r="D79" s="62">
+      <c r="D79" s="21">
         <f>SUM(D74:D78)</f>
         <v/>
       </c>
-      <c r="E79" s="63">
+      <c r="E79" s="22">
         <f>IFERROR(D79/C79,"")</f>
         <v/>
       </c>
-      <c r="F79" s="62">
+      <c r="F79" s="21">
         <f>SUM(F74:F78)</f>
         <v/>
       </c>
       <c r="G79" s="23" t="inlineStr"/>
     </row>
+    <row r="80"/>
     <row r="81">
-      <c r="B81" s="35" t="inlineStr">
+      <c r="B81" s="34" t="inlineStr">
         <is>
           <t>SEPTIEMBRE</t>
         </is>
       </c>
-      <c r="C81" s="46" t="n"/>
-      <c r="D81" s="46" t="n"/>
-      <c r="E81" s="46" t="n"/>
-      <c r="F81" s="46" t="n"/>
-      <c r="G81" s="46" t="n"/>
+      <c r="C81" s="45" t="n"/>
+      <c r="D81" s="45" t="n"/>
+      <c r="E81" s="45" t="n"/>
+      <c r="F81" s="45" t="n"/>
+      <c r="G81" s="45" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" s="47" t="inlineStr">
+      <c r="B82" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C82" s="47" t="inlineStr">
+      <c r="C82" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D82" s="47" t="inlineStr">
+      <c r="D82" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E82" s="47" t="inlineStr">
+      <c r="E82" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F82" s="47" t="inlineStr">
+      <c r="F82" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G82" s="47" t="inlineStr">
+      <c r="G82" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="55" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C83" s="60" t="n">
+      <c r="C83" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D83" s="48" t="n"/>
-      <c r="E83" s="61">
+      <c r="D83" s="47" t="n"/>
+      <c r="E83" s="10">
         <f>IFERROR(D83/C83,"")</f>
         <v/>
       </c>
-      <c r="F83" s="48" t="n"/>
+      <c r="F83" s="47" t="n"/>
       <c r="G83" s="25" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" s="55" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C84" s="60" t="n">
+      <c r="C84" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D84" s="48" t="n"/>
-      <c r="E84" s="61">
+      <c r="D84" s="47" t="n"/>
+      <c r="E84" s="10">
         <f>IFERROR(D84/C84,"")</f>
         <v/>
       </c>
-      <c r="F84" s="48" t="n"/>
+      <c r="F84" s="47" t="n"/>
       <c r="G84" s="25" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" s="55" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C85" s="60" t="n">
+      <c r="C85" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D85" s="48" t="n"/>
-      <c r="E85" s="61">
+      <c r="D85" s="47" t="n"/>
+      <c r="E85" s="10">
         <f>IFERROR(D85/C85,"")</f>
         <v/>
       </c>
-      <c r="F85" s="48" t="n"/>
+      <c r="F85" s="47" t="n"/>
       <c r="G85" s="25" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="55" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C86" s="60" t="n">
+      <c r="C86" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D86" s="48" t="n"/>
-      <c r="E86" s="61">
+      <c r="D86" s="47" t="n"/>
+      <c r="E86" s="10">
         <f>IFERROR(D86/C86,"")</f>
         <v/>
       </c>
-      <c r="F86" s="48" t="n"/>
+      <c r="F86" s="47" t="n"/>
       <c r="G86" s="25" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="55" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C87" s="60" t="n">
+      <c r="C87" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D87" s="48" t="n"/>
-      <c r="E87" s="61">
+      <c r="D87" s="47" t="n"/>
+      <c r="E87" s="10">
         <f>IFERROR(D87/C87,"")</f>
         <v/>
       </c>
-      <c r="F87" s="48" t="n"/>
+      <c r="F87" s="47" t="n"/>
       <c r="G87" s="25" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="53" t="inlineStr">
+      <c r="B88" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C88" s="62">
+      <c r="C88" s="21">
         <f>SUM(C83:C87)</f>
         <v/>
       </c>
-      <c r="D88" s="62">
+      <c r="D88" s="21">
         <f>SUM(D83:D87)</f>
         <v/>
       </c>
-      <c r="E88" s="63">
+      <c r="E88" s="22">
         <f>IFERROR(D88/C88,"")</f>
         <v/>
       </c>
-      <c r="F88" s="62">
+      <c r="F88" s="21">
         <f>SUM(F83:F87)</f>
         <v/>
       </c>
       <c r="G88" s="23" t="inlineStr"/>
     </row>
+    <row r="89"/>
     <row r="90">
-      <c r="B90" s="35" t="inlineStr">
+      <c r="B90" s="34" t="inlineStr">
         <is>
           <t>OCTUBRE</t>
         </is>
       </c>
-      <c r="C90" s="46" t="n"/>
-      <c r="D90" s="46" t="n"/>
-      <c r="E90" s="46" t="n"/>
-      <c r="F90" s="46" t="n"/>
-      <c r="G90" s="46" t="n"/>
+      <c r="C90" s="45" t="n"/>
+      <c r="D90" s="45" t="n"/>
+      <c r="E90" s="45" t="n"/>
+      <c r="F90" s="45" t="n"/>
+      <c r="G90" s="45" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="47" t="inlineStr">
+      <c r="B91" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C91" s="47" t="inlineStr">
+      <c r="C91" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D91" s="47" t="inlineStr">
+      <c r="D91" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E91" s="47" t="inlineStr">
+      <c r="E91" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F91" s="47" t="inlineStr">
+      <c r="F91" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G91" s="47" t="inlineStr">
+      <c r="G91" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="55" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C92" s="60" t="n">
+      <c r="C92" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D92" s="48" t="n"/>
-      <c r="E92" s="61">
+      <c r="D92" s="47" t="n"/>
+      <c r="E92" s="10">
         <f>IFERROR(D92/C92,"")</f>
         <v/>
       </c>
-      <c r="F92" s="48" t="n"/>
+      <c r="F92" s="47" t="n"/>
       <c r="G92" s="25" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="55" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C93" s="60" t="n">
+      <c r="C93" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D93" s="48" t="n"/>
-      <c r="E93" s="61">
+      <c r="D93" s="47" t="n"/>
+      <c r="E93" s="10">
         <f>IFERROR(D93/C93,"")</f>
         <v/>
       </c>
-      <c r="F93" s="48" t="n"/>
+      <c r="F93" s="47" t="n"/>
       <c r="G93" s="25" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="55" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C94" s="60" t="n">
+      <c r="C94" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D94" s="48" t="n"/>
-      <c r="E94" s="61">
+      <c r="D94" s="47" t="n"/>
+      <c r="E94" s="10">
         <f>IFERROR(D94/C94,"")</f>
         <v/>
       </c>
-      <c r="F94" s="48" t="n"/>
+      <c r="F94" s="47" t="n"/>
       <c r="G94" s="25" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="55" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C95" s="60" t="n">
+      <c r="C95" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D95" s="48" t="n"/>
-      <c r="E95" s="61">
+      <c r="D95" s="47" t="n"/>
+      <c r="E95" s="10">
         <f>IFERROR(D95/C95,"")</f>
         <v/>
       </c>
-      <c r="F95" s="48" t="n"/>
+      <c r="F95" s="47" t="n"/>
       <c r="G95" s="25" t="n"/>
     </row>
     <row r="96">
-      <c r="B96" s="55" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C96" s="60" t="n">
+      <c r="C96" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D96" s="48" t="n"/>
-      <c r="E96" s="61">
+      <c r="D96" s="47" t="n"/>
+      <c r="E96" s="10">
         <f>IFERROR(D96/C96,"")</f>
         <v/>
       </c>
-      <c r="F96" s="48" t="n"/>
+      <c r="F96" s="47" t="n"/>
       <c r="G96" s="25" t="n"/>
     </row>
     <row r="97">
-      <c r="B97" s="53" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C97" s="62">
+      <c r="C97" s="21">
         <f>SUM(C92:C96)</f>
         <v/>
       </c>
-      <c r="D97" s="62">
+      <c r="D97" s="21">
         <f>SUM(D92:D96)</f>
         <v/>
       </c>
-      <c r="E97" s="63">
+      <c r="E97" s="22">
         <f>IFERROR(D97/C97,"")</f>
         <v/>
       </c>
-      <c r="F97" s="62">
+      <c r="F97" s="21">
         <f>SUM(F92:F96)</f>
         <v/>
       </c>
       <c r="G97" s="23" t="inlineStr"/>
     </row>
+    <row r="98"/>
     <row r="99">
-      <c r="B99" s="35" t="inlineStr">
+      <c r="B99" s="34" t="inlineStr">
         <is>
           <t>NOVIEMBRE</t>
         </is>
       </c>
-      <c r="C99" s="46" t="n"/>
-      <c r="D99" s="46" t="n"/>
-      <c r="E99" s="46" t="n"/>
-      <c r="F99" s="46" t="n"/>
-      <c r="G99" s="46" t="n"/>
+      <c r="C99" s="45" t="n"/>
+      <c r="D99" s="45" t="n"/>
+      <c r="E99" s="45" t="n"/>
+      <c r="F99" s="45" t="n"/>
+      <c r="G99" s="45" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="47" t="inlineStr">
+      <c r="B100" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C100" s="47" t="inlineStr">
+      <c r="C100" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D100" s="47" t="inlineStr">
+      <c r="D100" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E100" s="47" t="inlineStr">
+      <c r="E100" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F100" s="47" t="inlineStr">
+      <c r="F100" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G100" s="47" t="inlineStr">
+      <c r="G100" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="55" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C101" s="60" t="n">
+      <c r="C101" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D101" s="48" t="n"/>
-      <c r="E101" s="61">
+      <c r="D101" s="47" t="n"/>
+      <c r="E101" s="10">
         <f>IFERROR(D101/C101,"")</f>
         <v/>
       </c>
-      <c r="F101" s="48" t="n"/>
+      <c r="F101" s="47" t="n"/>
       <c r="G101" s="25" t="n"/>
     </row>
     <row r="102">
-      <c r="B102" s="55" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C102" s="60" t="n">
+      <c r="C102" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D102" s="48" t="n"/>
-      <c r="E102" s="61">
+      <c r="D102" s="47" t="n"/>
+      <c r="E102" s="10">
         <f>IFERROR(D102/C102,"")</f>
         <v/>
       </c>
-      <c r="F102" s="48" t="n"/>
+      <c r="F102" s="47" t="n"/>
       <c r="G102" s="25" t="n"/>
     </row>
     <row r="103">
-      <c r="B103" s="55" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C103" s="60" t="n">
+      <c r="C103" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D103" s="48" t="n"/>
-      <c r="E103" s="61">
+      <c r="D103" s="47" t="n"/>
+      <c r="E103" s="10">
         <f>IFERROR(D103/C103,"")</f>
         <v/>
       </c>
-      <c r="F103" s="48" t="n"/>
+      <c r="F103" s="47" t="n"/>
       <c r="G103" s="25" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="55" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C104" s="60" t="n">
+      <c r="C104" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D104" s="48" t="n"/>
-      <c r="E104" s="61">
+      <c r="D104" s="47" t="n"/>
+      <c r="E104" s="10">
         <f>IFERROR(D104/C104,"")</f>
         <v/>
       </c>
-      <c r="F104" s="48" t="n"/>
+      <c r="F104" s="47" t="n"/>
       <c r="G104" s="25" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="55" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C105" s="60" t="n">
+      <c r="C105" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D105" s="48" t="n"/>
-      <c r="E105" s="61">
+      <c r="D105" s="47" t="n"/>
+      <c r="E105" s="10">
         <f>IFERROR(D105/C105,"")</f>
         <v/>
       </c>
-      <c r="F105" s="48" t="n"/>
+      <c r="F105" s="47" t="n"/>
       <c r="G105" s="25" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="53" t="inlineStr">
+      <c r="B106" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C106" s="62">
+      <c r="C106" s="21">
         <f>SUM(C101:C105)</f>
         <v/>
       </c>
-      <c r="D106" s="62">
+      <c r="D106" s="21">
         <f>SUM(D101:D105)</f>
         <v/>
       </c>
-      <c r="E106" s="63">
+      <c r="E106" s="22">
         <f>IFERROR(D106/C106,"")</f>
         <v/>
       </c>
-      <c r="F106" s="62">
+      <c r="F106" s="21">
         <f>SUM(F101:F105)</f>
         <v/>
       </c>
       <c r="G106" s="23" t="inlineStr"/>
     </row>
+    <row r="107"/>
     <row r="108">
-      <c r="B108" s="35" t="inlineStr">
+      <c r="B108" s="34" t="inlineStr">
         <is>
           <t>DICIEMBRE</t>
         </is>
       </c>
-      <c r="C108" s="46" t="n"/>
-      <c r="D108" s="46" t="n"/>
-      <c r="E108" s="46" t="n"/>
-      <c r="F108" s="46" t="n"/>
-      <c r="G108" s="46" t="n"/>
+      <c r="C108" s="45" t="n"/>
+      <c r="D108" s="45" t="n"/>
+      <c r="E108" s="45" t="n"/>
+      <c r="F108" s="45" t="n"/>
+      <c r="G108" s="45" t="n"/>
     </row>
     <row r="109">
-      <c r="B109" s="47" t="inlineStr">
+      <c r="B109" s="46" t="inlineStr">
         <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="C109" s="47" t="inlineStr">
+      <c r="C109" s="46" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D109" s="47" t="inlineStr">
+      <c r="D109" s="46" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E109" s="47" t="inlineStr">
+      <c r="E109" s="46" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F109" s="47" t="inlineStr">
+      <c r="F109" s="46" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
-      <c r="G109" s="47" t="inlineStr">
+      <c r="G109" s="46" t="inlineStr">
         <is>
           <t>Observación</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="55" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>Isnardi Sanches</t>
         </is>
       </c>
-      <c r="C110" s="60" t="n">
+      <c r="C110" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D110" s="48" t="n"/>
-      <c r="E110" s="61">
+      <c r="D110" s="47" t="n"/>
+      <c r="E110" s="10">
         <f>IFERROR(D110/C110,"")</f>
         <v/>
       </c>
-      <c r="F110" s="48" t="n"/>
+      <c r="F110" s="47" t="n"/>
       <c r="G110" s="25" t="n"/>
     </row>
     <row r="111">
-      <c r="B111" s="55" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>Luis Amador</t>
         </is>
       </c>
-      <c r="C111" s="60" t="n">
+      <c r="C111" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D111" s="48" t="n"/>
-      <c r="E111" s="61">
+      <c r="D111" s="47" t="n"/>
+      <c r="E111" s="10">
         <f>IFERROR(D111/C111,"")</f>
         <v/>
       </c>
-      <c r="F111" s="48" t="n"/>
+      <c r="F111" s="47" t="n"/>
       <c r="G111" s="25" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="55" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>Cristian Bernal</t>
         </is>
       </c>
-      <c r="C112" s="60" t="n">
+      <c r="C112" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D112" s="48" t="n"/>
-      <c r="E112" s="61">
+      <c r="D112" s="47" t="n"/>
+      <c r="E112" s="10">
         <f>IFERROR(D112/C112,"")</f>
         <v/>
       </c>
-      <c r="F112" s="48" t="n"/>
+      <c r="F112" s="47" t="n"/>
       <c r="G112" s="25" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="55" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>Beatriz</t>
         </is>
       </c>
-      <c r="C113" s="60" t="n">
+      <c r="C113" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D113" s="48" t="n"/>
-      <c r="E113" s="61">
+      <c r="D113" s="47" t="n"/>
+      <c r="E113" s="10">
         <f>IFERROR(D113/C113,"")</f>
         <v/>
       </c>
-      <c r="F113" s="48" t="n"/>
+      <c r="F113" s="47" t="n"/>
       <c r="G113" s="25" t="n"/>
     </row>
     <row r="114">
-      <c r="B114" s="55" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>Edgar Metaute</t>
         </is>
       </c>
-      <c r="C114" s="60" t="n">
+      <c r="C114" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D114" s="48" t="n"/>
-      <c r="E114" s="61">
+      <c r="D114" s="47" t="n"/>
+      <c r="E114" s="10">
         <f>IFERROR(D114/C114,"")</f>
         <v/>
       </c>
-      <c r="F114" s="48" t="n"/>
+      <c r="F114" s="47" t="n"/>
       <c r="G114" s="25" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="53" t="inlineStr">
+      <c r="B115" s="20" t="inlineStr">
         <is>
           <t>Total equipo</t>
         </is>
       </c>
-      <c r="C115" s="62">
+      <c r="C115" s="21">
         <f>SUM(C110:C114)</f>
         <v/>
       </c>
-      <c r="D115" s="62">
+      <c r="D115" s="21">
         <f>SUM(D110:D114)</f>
         <v/>
       </c>
-      <c r="E115" s="63">
+      <c r="E115" s="22">
         <f>IFERROR(D115/C115,"")</f>
         <v/>
       </c>
-      <c r="F115" s="62">
+      <c r="F115" s="21">
         <f>SUM(F110:F114)</f>
         <v/>
       </c>
@@ -5643,7 +5631,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5676,34 +5664,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="59" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Programadas</t>
         </is>
       </c>
-      <c r="D4" s="59" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Completadas</t>
         </is>
       </c>
-      <c r="E4" s="59" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Cumplimiento</t>
         </is>
       </c>
-      <c r="F4" s="59" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Vencidas</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="55" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
@@ -5716,7 +5704,7 @@
         <f>'4 Gestion mensual'!D16</f>
         <v/>
       </c>
-      <c r="E5" s="61">
+      <c r="E5" s="77">
         <f>IFERROR(D5/C5,"")</f>
         <v/>
       </c>
@@ -5726,7 +5714,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="55" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
@@ -5739,7 +5727,7 @@
         <f>'4 Gestion mensual'!D25</f>
         <v/>
       </c>
-      <c r="E6" s="61">
+      <c r="E6" s="77">
         <f>IFERROR(D6/C6,"")</f>
         <v/>
       </c>
@@ -5749,7 +5737,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="55" t="inlineStr">
+      <c r="B7" s="54" t="inlineStr">
         <is>
           <t>Marzo</t>
         </is>
@@ -5762,7 +5750,7 @@
         <f>'4 Gestion mensual'!D34</f>
         <v/>
       </c>
-      <c r="E7" s="61">
+      <c r="E7" s="77">
         <f>IFERROR(D7/C7,"")</f>
         <v/>
       </c>
@@ -5772,7 +5760,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="55" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
@@ -5785,7 +5773,7 @@
         <f>'4 Gestion mensual'!D43</f>
         <v/>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="77">
         <f>IFERROR(D8/C8,"")</f>
         <v/>
       </c>
@@ -5795,7 +5783,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="55" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
@@ -5808,7 +5796,7 @@
         <f>'4 Gestion mensual'!D52</f>
         <v/>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="77">
         <f>IFERROR(D9/C9,"")</f>
         <v/>
       </c>
@@ -5818,7 +5806,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="55" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
@@ -5831,7 +5819,7 @@
         <f>'4 Gestion mensual'!D61</f>
         <v/>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="77">
         <f>IFERROR(D10/C10,"")</f>
         <v/>
       </c>
@@ -5841,7 +5829,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="55" t="inlineStr">
+      <c r="B11" s="54" t="inlineStr">
         <is>
           <t>Julio</t>
         </is>
@@ -5854,7 +5842,7 @@
         <f>'4 Gestion mensual'!D70</f>
         <v/>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="77">
         <f>IFERROR(D11/C11,"")</f>
         <v/>
       </c>
@@ -5864,7 +5852,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="55" t="inlineStr">
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
@@ -5877,7 +5865,7 @@
         <f>'4 Gestion mensual'!D79</f>
         <v/>
       </c>
-      <c r="E12" s="61">
+      <c r="E12" s="77">
         <f>IFERROR(D12/C12,"")</f>
         <v/>
       </c>
@@ -5887,7 +5875,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="55" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
@@ -5900,7 +5888,7 @@
         <f>'4 Gestion mensual'!D88</f>
         <v/>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="77">
         <f>IFERROR(D13/C13,"")</f>
         <v/>
       </c>
@@ -5910,7 +5898,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="55" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
@@ -5923,7 +5911,7 @@
         <f>'4 Gestion mensual'!D97</f>
         <v/>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="77">
         <f>IFERROR(D14/C14,"")</f>
         <v/>
       </c>
@@ -5933,7 +5921,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="55" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
@@ -5946,7 +5934,7 @@
         <f>'4 Gestion mensual'!D106</f>
         <v/>
       </c>
-      <c r="E15" s="61">
+      <c r="E15" s="77">
         <f>IFERROR(D15/C15,"")</f>
         <v/>
       </c>
@@ -5956,7 +5944,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="55" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
@@ -5969,7 +5957,7 @@
         <f>'4 Gestion mensual'!D115</f>
         <v/>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="77">
         <f>IFERROR(D16/C16,"")</f>
         <v/>
       </c>
@@ -5979,30 +5967,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="53" t="inlineStr">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>TOTAL AÑO</t>
         </is>
       </c>
-      <c r="C17" s="62">
+      <c r="C17" s="73">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="73">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="63">
+      <c r="E17" s="78">
         <f>IFERROR(D17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="62">
+      <c r="F17" s="73">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="64" t="inlineStr">
+      <c r="B20" s="76" t="inlineStr">
         <is>
           <t>Las celdas de esta hoja se calculan solas. Para que muestren datos, diligencie primero la hoja 4.</t>
         </is>
@@ -6010,6 +5998,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/ies-procesos/Informes-Gerencia-IES-2026.xlsx
+++ b/ies-procesos/Informes-Gerencia-IES-2026.xlsx
@@ -376,11 +376,11 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -493,10 +493,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1255,16 +1255,16 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1196</v>
+        <v>1076</v>
       </c>
       <c r="F6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>5</v>
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>1003</v>
+        <v>1063</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>4</v>
@@ -1370,13 +1370,13 @@
         <v>60</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.5726027397260274</v>
+        <v>0.389041095890411</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>0.74</v>
+        <v>0.49</v>
       </c>
       <c r="H10" s="17" t="n">
         <v>2</v>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>0.2036363636363636</v>
+        <v>0.1793893129770992</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>85</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>0.3090909090909091</v>
+        <v>0.3244274809160305</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>47</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>0.1709090909090909</v>
+        <v>0.1793893129770992</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.2181818181818182</v>
+        <v>0.2175572519083969</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.09818181818181818</v>
+        <v>0.09923664122137404</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D20" s="22" t="n">
         <v>1</v>
@@ -1736,43 +1736,43 @@
         </is>
       </c>
       <c r="C6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="J6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K6" s="28" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="M6" s="28" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>1196</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="7">
@@ -1782,85 +1782,85 @@
         </is>
       </c>
       <c r="C7" s="28" t="n">
-        <v>85</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>76</v>
+        <v>90</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>81</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J7" s="28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K7" s="28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L7" s="28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M7" s="28" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O7" s="21" t="n">
-        <v>1003</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Cristian</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="K8" s="30" t="n">
+      <c r="K8" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="L8" s="30" t="n">
+      <c r="L8" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="M8" s="30" t="n">
+      <c r="M8" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="N8" s="30" t="n">
+      <c r="N8" s="31" t="n">
         <v>58</v>
       </c>
       <c r="O8" s="21" t="n">
@@ -1920,43 +1920,43 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="O10" s="21" t="n">
-        <v>269</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -1966,43 +1966,43 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="H11" s="21" t="n">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="I11" s="21" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="J11" s="21" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="K11" s="21" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="L11" s="21" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="M11" s="21" t="n">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="N11" s="21" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="O11" s="21" t="n">
-        <v>3283</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="14">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3.29</v>
+        <v>2.97</v>
       </c>
       <c r="G16" s="35" t="n">
         <v>5</v>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="G17" s="35" t="n">
         <v>4</v>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>18 de 31</t>
+          <t>12 de 31</t>
         </is>
       </c>
       <c r="E20" s="10" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="G20" s="38" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="36" t="inlineStr">
         <is>
-          <t>1, 2, 3, 4, 5</t>
+          <t>1, 2, 3</t>
         </is>
       </c>
     </row>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="C6" s="58" t="n">
-        <v>4.58</v>
+        <v>4.12</v>
       </c>
       <c r="D6" s="59" t="n">
-        <v>365</v>
+        <v>305</v>
       </c>
       <c r="E6" s="60" t="n">
         <v>77</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="C7" s="58" t="n">
-        <v>3.84</v>
+        <v>4.07</v>
       </c>
       <c r="D7" s="61" t="n">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="E7" s="60" t="n">
         <v>71</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="C10" s="63" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="D10" s="61" t="n">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="60" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
@@ -2513,43 +2513,43 @@
         </is>
       </c>
       <c r="C15" s="64" t="n">
-        <v>4.64</v>
+        <v>4.18</v>
       </c>
       <c r="D15" s="64" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="64" t="n">
-        <v>4.64</v>
+        <v>4.18</v>
       </c>
       <c r="F15" s="64" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="G15" s="64" t="n">
-        <v>4.86</v>
+        <v>4.38</v>
       </c>
       <c r="H15" s="64" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="I15" s="64" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="J15" s="64" t="n">
-        <v>4.86</v>
+        <v>4.38</v>
       </c>
       <c r="K15" s="64" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="L15" s="64" t="n">
-        <v>4.64</v>
+        <v>4.18</v>
       </c>
       <c r="M15" s="64" t="n">
-        <v>4.67</v>
+        <v>4.19</v>
       </c>
       <c r="N15" s="64" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="O15" s="65" t="n">
-        <v>4.58</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="16">
@@ -2559,43 +2559,43 @@
         </is>
       </c>
       <c r="C16" s="64" t="n">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="D16" s="64" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="E16" s="64" t="n">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="F16" s="64" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="G16" s="64" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="H16" s="64" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="I16" s="64" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="J16" s="64" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="L16" s="64" t="n">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="M16" s="64" t="n">
-        <v>3.95</v>
+        <v>4.19</v>
       </c>
       <c r="N16" s="64" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="O16" s="65" t="n">
-        <v>3.84</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="17">
@@ -2697,43 +2697,43 @@
         </is>
       </c>
       <c r="C19" s="67" t="n">
-        <v>1.05</v>
+        <v>0.68</v>
       </c>
       <c r="D19" s="67" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="E19" s="67" t="n">
-        <v>1.05</v>
+        <v>0.68</v>
       </c>
       <c r="F19" s="67" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="G19" s="67" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="H19" s="67" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="I19" s="67" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="J19" s="67" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="K19" s="67" t="n">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="L19" s="67" t="n">
-        <v>1.05</v>
+        <v>0.68</v>
       </c>
       <c r="M19" s="67" t="n">
-        <v>1.05</v>
+        <v>0.71</v>
       </c>
       <c r="N19" s="67" t="n">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="O19" s="65" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="20">
@@ -2743,43 +2743,43 @@
         </is>
       </c>
       <c r="C20" s="69" t="n">
-        <v>12.82</v>
+        <v>12.23</v>
       </c>
       <c r="D20" s="69" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" s="69" t="n">
-        <v>12.82</v>
+        <v>12.23</v>
       </c>
       <c r="F20" s="69" t="n">
-        <v>12.14</v>
+        <v>11.59</v>
       </c>
       <c r="G20" s="69" t="n">
-        <v>13.43</v>
+        <v>12.81</v>
       </c>
       <c r="H20" s="69" t="n">
-        <v>12.14</v>
+        <v>11.59</v>
       </c>
       <c r="I20" s="69" t="n">
-        <v>12.26</v>
+        <v>11.7</v>
       </c>
       <c r="J20" s="69" t="n">
-        <v>13.1</v>
+        <v>12.48</v>
       </c>
       <c r="K20" s="69" t="n">
-        <v>12.45</v>
+        <v>11.91</v>
       </c>
       <c r="L20" s="69" t="n">
-        <v>12.5</v>
+        <v>11.91</v>
       </c>
       <c r="M20" s="69" t="n">
-        <v>13.05</v>
+        <v>12.48</v>
       </c>
       <c r="N20" s="69" t="n">
-        <v>11.96</v>
+        <v>11.39</v>
       </c>
       <c r="O20" s="65" t="n">
-        <v>12.59</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="21">
@@ -2913,44 +2913,44 @@
           <t>Isnardi</t>
         </is>
       </c>
-      <c r="C25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="D25" s="59" t="n">
-        <v>28</v>
-      </c>
-      <c r="E25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="F25" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="G25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="H25" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="J25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="K25" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="L25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="M25" s="59" t="n">
-        <v>30</v>
-      </c>
-      <c r="N25" s="59" t="n">
-        <v>31</v>
-      </c>
-      <c r="O25" s="73" t="n">
-        <v>365</v>
+      <c r="C25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" s="73" t="n">
+        <v>23</v>
+      </c>
+      <c r="E25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="F25" s="73" t="n">
+        <v>25</v>
+      </c>
+      <c r="G25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="H25" s="73" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="J25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="K25" s="73" t="n">
+        <v>25</v>
+      </c>
+      <c r="L25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="M25" s="73" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" s="73" t="n">
+        <v>26</v>
+      </c>
+      <c r="O25" s="74" t="n">
+        <v>305</v>
       </c>
     </row>
     <row r="26">
@@ -2959,44 +2959,44 @@
           <t>Luis</t>
         </is>
       </c>
-      <c r="C26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="D26" s="74" t="n">
-        <v>15</v>
-      </c>
-      <c r="E26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="F26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="G26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="H26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="I26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="K26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="L26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="M26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="N26" s="74" t="n">
-        <v>17</v>
-      </c>
-      <c r="O26" s="73" t="n">
-        <v>202</v>
+      <c r="C26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" s="73" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="G26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="H26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="J26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="K26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="L26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="M26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="N26" s="73" t="n">
+        <v>22</v>
+      </c>
+      <c r="O26" s="74" t="n">
+        <v>262</v>
       </c>
     </row>
     <row r="27">
@@ -3041,7 +3041,7 @@
       <c r="N27" s="60" t="n">
         <v>6</v>
       </c>
-      <c r="O27" s="73" t="n">
+      <c r="O27" s="74" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
     <row r="31">
       <c r="B31" s="55" t="inlineStr">
         <is>
-          <t>·  Tesorería registra 3 o más frentes abiertos 365 de los 365 días del año, incluidos los 104 días de fin de semana.</t>
+          <t>·  Tesorería registra 3 o más frentes abiertos 305 de los 365 días del año, incluidos los 104 días de fin de semana.</t>
         </is>
       </c>
     </row>
@@ -3069,14 +3069,14 @@
     <row r="33">
       <c r="B33" s="55" t="inlineStr">
         <is>
-          <t>·  El Auxiliar Contable está en esa condición 202 días al año; Contaduría 84 días, de ellos 48 con cuatro o más.</t>
+          <t>·  El Auxiliar Contable está en esa condición 262 días al año; Contaduría 84 días, de ellos 48 con cuatro o más.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="55" t="inlineStr">
         <is>
-          <t>·  El equipo sostiene entre 12 y 13 frentes por día hábil todos los meses: no hay temporada baja.</t>
+          <t>·  El equipo sostiene entre 11 y 13 frentes por día hábil todos los meses: no hay temporada baja.</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="47" t="n"/>
       <c r="E11" s="10">
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="47" t="n"/>
       <c r="E12" s="10">
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="47" t="n"/>
       <c r="E20" s="10">
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="47" t="n"/>
       <c r="E21" s="10">
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="C29" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="47" t="n"/>
       <c r="E29" s="10">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" s="47" t="n"/>
       <c r="E30" s="10">
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" s="47" t="n"/>
       <c r="E38" s="10">
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="C39" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D39" s="47" t="n"/>
       <c r="E39" s="10">
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="C47" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" s="47" t="n"/>
       <c r="E47" s="10">
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D48" s="47" t="n"/>
       <c r="E48" s="10">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56" s="47" t="n"/>
       <c r="E56" s="10">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C57" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D57" s="47" t="n"/>
       <c r="E57" s="10">
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="C65" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D65" s="47" t="n"/>
       <c r="E65" s="10">
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D66" s="47" t="n"/>
       <c r="E66" s="10">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D74" s="47" t="n"/>
       <c r="E74" s="10">
@@ -4920,7 +4920,7 @@
         </is>
       </c>
       <c r="C75" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" s="47" t="n"/>
       <c r="E75" s="10">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="C83" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" s="47" t="n"/>
       <c r="E83" s="10">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D84" s="47" t="n"/>
       <c r="E84" s="10">
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D92" s="47" t="n"/>
       <c r="E92" s="10">
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="C93" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D93" s="47" t="n"/>
       <c r="E93" s="10">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="C101" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D101" s="47" t="n"/>
       <c r="E101" s="10">
@@ -5382,7 +5382,7 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D102" s="47" t="n"/>
       <c r="E102" s="10">
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D110" s="47" t="n"/>
       <c r="E110" s="10">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="C111" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D111" s="47" t="n"/>
       <c r="E111" s="10">
@@ -5972,11 +5972,11 @@
           <t>TOTAL AÑO</t>
         </is>
       </c>
-      <c r="C17" s="73">
+      <c r="C17" s="74">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="74">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
@@ -5984,7 +5984,7 @@
         <f>IFERROR(D17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="73">
+      <c r="F17" s="74">
         <f>SUM(F5:F16)</f>
         <v/>
       </c>
